--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2390,7 +2390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4401,6 +4401,44 @@
       </c>
       <c r="I53" s="3">
         <f>F53/H53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D54" s="23" t="n">
+        <v>46276</v>
+      </c>
+      <c r="E54" t="n">
+        <v>626241.66</v>
+      </c>
+      <c r="F54">
+        <f>E54-E53</f>
+        <v/>
+      </c>
+      <c r="G54">
+        <f>F54/E53</f>
+        <v/>
+      </c>
+      <c r="H54" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I54">
+        <f>F54/H54</f>
         <v/>
       </c>
     </row>
@@ -6432,11 +6470,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续3日减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-3+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6473,11 +6511,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>连续2日增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-1+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-2+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6492,7 +6530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8506,6 +8544,44 @@
         <v/>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D54" s="23" t="n">
+        <v>46276</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1968245.49</v>
+      </c>
+      <c r="F54">
+        <f>E54-E53</f>
+        <v/>
+      </c>
+      <c r="G54">
+        <f>F54/E53</f>
+        <v/>
+      </c>
+      <c r="H54" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I54">
+        <f>F54/H54</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2376,6 +2376,44 @@
       </c>
       <c r="I48" s="3">
         <f>F48/H48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D49" s="23" t="n">
+        <v>46276</v>
+      </c>
+      <c r="E49" t="n">
+        <v>703146.6800000001</v>
+      </c>
+      <c r="F49">
+        <f>E49-E48</f>
+        <v/>
+      </c>
+      <c r="G49">
+        <f>F49/E48</f>
+        <v/>
+      </c>
+      <c r="H49" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I49">
+        <f>F49/H49</f>
         <v/>
       </c>
     </row>
@@ -4405,17 +4443,17 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -4423,21 +4461,21 @@
       <c r="D54" s="23" t="n">
         <v>46276</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" s="3" t="n">
         <v>626241.66</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="3">
         <f>E54-E53</f>
         <v/>
       </c>
-      <c r="G54">
+      <c r="G54" s="3">
         <f>F54/E53</f>
         <v/>
       </c>
-      <c r="H54" t="n">
+      <c r="H54" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I54">
+      <c r="I54" s="3">
         <f>F54/H54</f>
         <v/>
       </c>
@@ -4453,7 +4491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -6286,6 +6324,44 @@
       </c>
       <c r="I48" s="3">
         <f>F48/H48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D49" s="23" t="n">
+        <v>46276</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2339868.77</v>
+      </c>
+      <c r="F49">
+        <f>E49-E48</f>
+        <v/>
+      </c>
+      <c r="G49">
+        <f>F49/E48</f>
+        <v/>
+      </c>
+      <c r="H49" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I49">
+        <f>F49/H49</f>
         <v/>
       </c>
     </row>
@@ -6388,11 +6464,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续3日减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-3+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-1+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6429,11 +6505,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>连续2日增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-1+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-2+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8545,17 +8621,17 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -8563,21 +8639,21 @@
       <c r="D54" s="23" t="n">
         <v>46276</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" s="3" t="n">
         <v>1968245.49</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="3">
         <f>E54-E53</f>
         <v/>
       </c>
-      <c r="G54">
+      <c r="G54" s="3">
         <f>F54/E53</f>
         <v/>
       </c>
-      <c r="H54" t="n">
+      <c r="H54" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I54">
+      <c r="I54" s="3">
         <f>F54/H54</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2380,17 +2380,17 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2398,22 +2398,60 @@
       <c r="D49" s="23" t="n">
         <v>46276</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="3" t="n">
         <v>703146.6800000001</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="3">
         <f>E49-E48</f>
         <v/>
       </c>
-      <c r="G49">
+      <c r="G49" s="3">
         <f>F49/E48</f>
         <v/>
       </c>
-      <c r="H49" t="n">
+      <c r="H49" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I49">
+      <c r="I49" s="3">
         <f>F49/H49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D50" s="23" t="n">
+        <v>46279</v>
+      </c>
+      <c r="E50" t="n">
+        <v>704676.6800000001</v>
+      </c>
+      <c r="F50">
+        <f>E50-E49</f>
+        <v/>
+      </c>
+      <c r="G50">
+        <f>F50/E49</f>
+        <v/>
+      </c>
+      <c r="H50" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I50">
+        <f>F50/H50</f>
         <v/>
       </c>
     </row>
@@ -2428,7 +2466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4477,6 +4515,44 @@
       </c>
       <c r="I54" s="3">
         <f>F54/H54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="n">
+        <v>46279</v>
+      </c>
+      <c r="E55" t="n">
+        <v>631101.66</v>
+      </c>
+      <c r="F55">
+        <f>E55-E54</f>
+        <v/>
+      </c>
+      <c r="G55">
+        <f>F55/E54</f>
+        <v/>
+      </c>
+      <c r="H55" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I55">
+        <f>F55/H55</f>
         <v/>
       </c>
     </row>
@@ -4491,7 +4567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -6328,17 +6404,17 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -6346,22 +6422,60 @@
       <c r="D49" s="23" t="n">
         <v>46276</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="3" t="n">
         <v>2339868.77</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="3">
         <f>E49-E48</f>
         <v/>
       </c>
-      <c r="G49">
+      <c r="G49" s="3">
         <f>F49/E48</f>
         <v/>
       </c>
-      <c r="H49" t="n">
+      <c r="H49" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I49">
+      <c r="I49" s="3">
         <f>F49/H49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D50" s="23" t="n">
+        <v>46279</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2340318.77</v>
+      </c>
+      <c r="F50">
+        <f>E50-E49</f>
+        <v/>
+      </c>
+      <c r="G50">
+        <f>F50/E49</f>
+        <v/>
+      </c>
+      <c r="H50" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I50">
+        <f>F50/H50</f>
         <v/>
       </c>
     </row>
@@ -6464,11 +6578,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>连续2日增持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-1+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-2+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6505,11 +6619,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续2日增持</t>
+          <t>连续3日增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-2+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-3+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6546,11 +6660,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>连续2日增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6587,11 +6701,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续2日增持</t>
+          <t>连续3日增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-2+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-3+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6606,7 +6720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8658,6 +8772,44 @@
         <v/>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="n">
+        <v>46279</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1977845.49</v>
+      </c>
+      <c r="F55">
+        <f>E55-E54</f>
+        <v/>
+      </c>
+      <c r="G55">
+        <f>F55/E54</f>
+        <v/>
+      </c>
+      <c r="H55" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I55">
+        <f>F55/H55</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2418,17 +2418,17 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2436,21 +2436,21 @@
       <c r="D50" s="23" t="n">
         <v>46279</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="3" t="n">
         <v>704676.6800000001</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="3">
         <f>E50-E49</f>
         <v/>
       </c>
-      <c r="G50">
+      <c r="G50" s="3">
         <f>F50/E49</f>
         <v/>
       </c>
-      <c r="H50" t="n">
+      <c r="H50" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I50">
+      <c r="I50" s="3">
         <f>F50/H50</f>
         <v/>
       </c>
@@ -4519,17 +4519,17 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -4537,21 +4537,21 @@
       <c r="D55" s="23" t="n">
         <v>46279</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="3" t="n">
         <v>631101.66</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="3">
         <f>E55-E54</f>
         <v/>
       </c>
-      <c r="G55">
+      <c r="G55" s="3">
         <f>F55/E54</f>
         <v/>
       </c>
-      <c r="H55" t="n">
+      <c r="H55" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I55">
+      <c r="I55" s="3">
         <f>F55/H55</f>
         <v/>
       </c>
@@ -6442,17 +6442,17 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -6460,21 +6460,21 @@
       <c r="D50" s="23" t="n">
         <v>46279</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="3" t="n">
         <v>2340318.77</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="3">
         <f>E50-E49</f>
         <v/>
       </c>
-      <c r="G50">
+      <c r="G50" s="3">
         <f>F50/E49</f>
         <v/>
       </c>
-      <c r="H50" t="n">
+      <c r="H50" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I50">
+      <c r="I50" s="3">
         <f>F50/H50</f>
         <v/>
       </c>
@@ -8773,17 +8773,17 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -8791,21 +8791,21 @@
       <c r="D55" s="23" t="n">
         <v>46279</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="3" t="n">
         <v>1977845.49</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="3">
         <f>E55-E54</f>
         <v/>
       </c>
-      <c r="G55">
+      <c r="G55" s="3">
         <f>F55/E54</f>
         <v/>
       </c>
-      <c r="H55" t="n">
+      <c r="H55" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I55">
+      <c r="I55" s="3">
         <f>F55/H55</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2452,6 +2452,44 @@
       </c>
       <c r="I50" s="3">
         <f>F50/H50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D51" s="23" t="n">
+        <v>46280</v>
+      </c>
+      <c r="E51" t="n">
+        <v>718986.6800000001</v>
+      </c>
+      <c r="F51">
+        <f>E51-E50</f>
+        <v/>
+      </c>
+      <c r="G51">
+        <f>F51/E50</f>
+        <v/>
+      </c>
+      <c r="H51" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I51">
+        <f>F51/H51</f>
         <v/>
       </c>
     </row>
@@ -2466,7 +2504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4553,6 +4591,44 @@
       </c>
       <c r="I55" s="3">
         <f>F55/H55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D56" s="23" t="n">
+        <v>46280</v>
+      </c>
+      <c r="E56" t="n">
+        <v>633711.66</v>
+      </c>
+      <c r="F56">
+        <f>E56-E55</f>
+        <v/>
+      </c>
+      <c r="G56">
+        <f>F56/E55</f>
+        <v/>
+      </c>
+      <c r="H56" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I56">
+        <f>F56/H56</f>
         <v/>
       </c>
     </row>
@@ -4567,7 +4643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -6476,6 +6552,44 @@
       </c>
       <c r="I50" s="3">
         <f>F50/H50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D51" s="23" t="n">
+        <v>46280</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2354268.77</v>
+      </c>
+      <c r="F51">
+        <f>E51-E50</f>
+        <v/>
+      </c>
+      <c r="G51">
+        <f>F51/E50</f>
+        <v/>
+      </c>
+      <c r="H51" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I51">
+        <f>F51/H51</f>
         <v/>
       </c>
     </row>
@@ -6578,11 +6692,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续2日增持</t>
+          <t>连续3日增持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-2+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-3+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6619,11 +6733,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续3日增持</t>
+          <t>连续4日增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-3+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-4+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6660,11 +6774,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续2日增持</t>
+          <t>连续3日增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-3+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6701,11 +6815,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续3日增持</t>
+          <t>连续4日增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-3+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-4+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6720,7 +6834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8810,6 +8924,44 @@
         <v/>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D56" s="23" t="n">
+        <v>46280</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2030545.49</v>
+      </c>
+      <c r="F56">
+        <f>E56-E55</f>
+        <v/>
+      </c>
+      <c r="G56">
+        <f>F56/E55</f>
+        <v/>
+      </c>
+      <c r="H56" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I56">
+        <f>F56/H56</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2456,17 +2456,17 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2474,21 +2474,21 @@
       <c r="D51" s="23" t="n">
         <v>46280</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="3" t="n">
         <v>718986.6800000001</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="3">
         <f>E51-E50</f>
         <v/>
       </c>
-      <c r="G51">
+      <c r="G51" s="3">
         <f>F51/E50</f>
         <v/>
       </c>
-      <c r="H51" t="n">
+      <c r="H51" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I51">
+      <c r="I51" s="3">
         <f>F51/H51</f>
         <v/>
       </c>
@@ -4595,17 +4595,17 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -4613,21 +4613,21 @@
       <c r="D56" s="23" t="n">
         <v>46280</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="3" t="n">
         <v>633711.66</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="3">
         <f>E56-E55</f>
         <v/>
       </c>
-      <c r="G56">
+      <c r="G56" s="3">
         <f>F56/E55</f>
         <v/>
       </c>
-      <c r="H56" t="n">
+      <c r="H56" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I56">
+      <c r="I56" s="3">
         <f>F56/H56</f>
         <v/>
       </c>
@@ -6556,17 +6556,17 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -6574,21 +6574,21 @@
       <c r="D51" s="23" t="n">
         <v>46280</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="3" t="n">
         <v>2354268.77</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="3">
         <f>E51-E50</f>
         <v/>
       </c>
-      <c r="G51">
+      <c r="G51" s="3">
         <f>F51/E50</f>
         <v/>
       </c>
-      <c r="H51" t="n">
+      <c r="H51" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I51">
+      <c r="I51" s="3">
         <f>F51/H51</f>
         <v/>
       </c>
@@ -8925,17 +8925,17 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -8943,21 +8943,21 @@
       <c r="D56" s="23" t="n">
         <v>46280</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="3" t="n">
         <v>2030545.49</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="3">
         <f>E56-E55</f>
         <v/>
       </c>
-      <c r="G56">
+      <c r="G56" s="3">
         <f>F56/E55</f>
         <v/>
       </c>
-      <c r="H56" t="n">
+      <c r="H56" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I56">
+      <c r="I56" s="3">
         <f>F56/H56</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2504,7 +2504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4629,6 +4629,44 @@
       </c>
       <c r="I56" s="3">
         <f>F56/H56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D57" s="23" t="n">
+        <v>46281</v>
+      </c>
+      <c r="E57" t="n">
+        <v>634161.66</v>
+      </c>
+      <c r="F57">
+        <f>E57-E56</f>
+        <v/>
+      </c>
+      <c r="G57">
+        <f>F57/E56</f>
+        <v/>
+      </c>
+      <c r="H57" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I57">
+        <f>F57/H57</f>
         <v/>
       </c>
     </row>
@@ -6774,11 +6812,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续3日增持</t>
+          <t>连续4日增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-3+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-4+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6815,11 +6853,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续4日增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-4+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-1+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6834,7 +6872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8962,6 +9000,44 @@
         <v/>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D57" s="23" t="n">
+        <v>46281</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2028345.49</v>
+      </c>
+      <c r="F57">
+        <f>E57-E56</f>
+        <v/>
+      </c>
+      <c r="G57">
+        <f>F57/E56</f>
+        <v/>
+      </c>
+      <c r="H57" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I57">
+        <f>F57/H57</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -4633,17 +4633,17 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -4651,21 +4651,21 @@
       <c r="D57" s="23" t="n">
         <v>46281</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" s="3" t="n">
         <v>634161.66</v>
       </c>
-      <c r="F57">
+      <c r="F57" s="3">
         <f>E57-E56</f>
         <v/>
       </c>
-      <c r="G57">
+      <c r="G57" s="3">
         <f>F57/E56</f>
         <v/>
       </c>
-      <c r="H57" t="n">
+      <c r="H57" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I57">
+      <c r="I57" s="3">
         <f>F57/H57</f>
         <v/>
       </c>
@@ -9001,17 +9001,17 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -9019,21 +9019,21 @@
       <c r="D57" s="23" t="n">
         <v>46281</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" s="3" t="n">
         <v>2028345.49</v>
       </c>
-      <c r="F57">
+      <c r="F57" s="3">
         <f>E57-E56</f>
         <v/>
       </c>
-      <c r="G57">
+      <c r="G57" s="3">
         <f>F57/E56</f>
         <v/>
       </c>
-      <c r="H57" t="n">
+      <c r="H57" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I57">
+      <c r="I57" s="3">
         <f>F57/H57</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2490,6 +2490,44 @@
       </c>
       <c r="I51" s="3">
         <f>F51/H51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D52" s="23" t="n">
+        <v>46282</v>
+      </c>
+      <c r="E52" t="n">
+        <v>779016.6800000001</v>
+      </c>
+      <c r="F52">
+        <f>E52-E51</f>
+        <v/>
+      </c>
+      <c r="G52">
+        <f>F52/E51</f>
+        <v/>
+      </c>
+      <c r="H52" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I52">
+        <f>F52/H52</f>
         <v/>
       </c>
     </row>
@@ -2504,7 +2542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4667,6 +4705,44 @@
       </c>
       <c r="I57" s="3">
         <f>F57/H57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D58" s="23" t="n">
+        <v>46282</v>
+      </c>
+      <c r="E58" t="n">
+        <v>634071.66</v>
+      </c>
+      <c r="F58">
+        <f>E58-E57</f>
+        <v/>
+      </c>
+      <c r="G58">
+        <f>F58/E57</f>
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I58">
+        <f>F58/H58</f>
         <v/>
       </c>
     </row>
@@ -4681,7 +4757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -6628,6 +6704,44 @@
       </c>
       <c r="I51" s="3">
         <f>F51/H51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D52" s="23" t="n">
+        <v>46282</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2370108.77</v>
+      </c>
+      <c r="F52">
+        <f>E52-E51</f>
+        <v/>
+      </c>
+      <c r="G52">
+        <f>F52/E51</f>
+        <v/>
+      </c>
+      <c r="H52" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I52">
+        <f>F52/H52</f>
         <v/>
       </c>
     </row>
@@ -6730,11 +6844,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续3日增持</t>
+          <t>连续4日增持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-3+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-4+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6771,11 +6885,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续4日增持</t>
+          <t>连续5日增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-4+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-5+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6812,11 +6926,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续4日增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-4+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6853,11 +6967,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>连续2日减持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-1+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-2+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6872,7 +6986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9038,6 +9152,44 @@
         <v/>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D58" s="23" t="n">
+        <v>46282</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1999545.49</v>
+      </c>
+      <c r="F58">
+        <f>E58-E57</f>
+        <v/>
+      </c>
+      <c r="G58">
+        <f>F58/E57</f>
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I58">
+        <f>F58/H58</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2494,17 +2494,17 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2512,21 +2512,21 @@
       <c r="D52" s="23" t="n">
         <v>46282</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="3" t="n">
         <v>779016.6800000001</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="3">
         <f>E52-E51</f>
         <v/>
       </c>
-      <c r="G52">
+      <c r="G52" s="3">
         <f>F52/E51</f>
         <v/>
       </c>
-      <c r="H52" t="n">
+      <c r="H52" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I52">
+      <c r="I52" s="3">
         <f>F52/H52</f>
         <v/>
       </c>
@@ -4709,17 +4709,17 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -4727,21 +4727,21 @@
       <c r="D58" s="23" t="n">
         <v>46282</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58" s="3" t="n">
         <v>634071.66</v>
       </c>
-      <c r="F58">
+      <c r="F58" s="3">
         <f>E58-E57</f>
         <v/>
       </c>
-      <c r="G58">
+      <c r="G58" s="3">
         <f>F58/E57</f>
         <v/>
       </c>
-      <c r="H58" t="n">
+      <c r="H58" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I58">
+      <c r="I58" s="3">
         <f>F58/H58</f>
         <v/>
       </c>
@@ -6708,17 +6708,17 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -6726,21 +6726,21 @@
       <c r="D52" s="23" t="n">
         <v>46282</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="3" t="n">
         <v>2370108.77</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="3">
         <f>E52-E51</f>
         <v/>
       </c>
-      <c r="G52">
+      <c r="G52" s="3">
         <f>F52/E51</f>
         <v/>
       </c>
-      <c r="H52" t="n">
+      <c r="H52" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I52">
+      <c r="I52" s="3">
         <f>F52/H52</f>
         <v/>
       </c>
@@ -9153,17 +9153,17 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -9171,21 +9171,21 @@
       <c r="D58" s="23" t="n">
         <v>46282</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58" s="3" t="n">
         <v>1999545.49</v>
       </c>
-      <c r="F58">
+      <c r="F58" s="3">
         <f>E58-E57</f>
         <v/>
       </c>
-      <c r="G58">
+      <c r="G58" s="3">
         <f>F58/E57</f>
         <v/>
       </c>
-      <c r="H58" t="n">
+      <c r="H58" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I58">
+      <c r="I58" s="3">
         <f>F58/H58</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2528,6 +2528,44 @@
       </c>
       <c r="I52" s="3">
         <f>F52/H52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D53" s="23" t="n">
+        <v>46283</v>
+      </c>
+      <c r="E53" t="n">
+        <v>796026.6800000001</v>
+      </c>
+      <c r="F53">
+        <f>E53-E52</f>
+        <v/>
+      </c>
+      <c r="G53">
+        <f>F53/E52</f>
+        <v/>
+      </c>
+      <c r="H53" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I53">
+        <f>F53/H53</f>
         <v/>
       </c>
     </row>
@@ -2542,7 +2580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4743,6 +4781,44 @@
       </c>
       <c r="I58" s="3">
         <f>F58/H58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D59" s="23" t="n">
+        <v>46283</v>
+      </c>
+      <c r="E59" t="n">
+        <v>632901.66</v>
+      </c>
+      <c r="F59">
+        <f>E59-E58</f>
+        <v/>
+      </c>
+      <c r="G59">
+        <f>F59/E58</f>
+        <v/>
+      </c>
+      <c r="H59" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I59">
+        <f>F59/H59</f>
         <v/>
       </c>
     </row>
@@ -4757,7 +4833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -6742,6 +6818,44 @@
       </c>
       <c r="I52" s="3">
         <f>F52/H52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D53" s="23" t="n">
+        <v>46283</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2365968.77</v>
+      </c>
+      <c r="F53">
+        <f>E53-E52</f>
+        <v/>
+      </c>
+      <c r="G53">
+        <f>F53/E52</f>
+        <v/>
+      </c>
+      <c r="H53" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I53">
+        <f>F53/H53</f>
         <v/>
       </c>
     </row>
@@ -6844,11 +6958,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续4日增持</t>
+          <t>连续5日增持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-4+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-5+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6885,11 +6999,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续5日增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-5+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-1+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6926,11 +7040,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>连续2日减持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6967,11 +7081,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续2日减持</t>
+          <t>连续3日减持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-2+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-3+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6986,7 +7100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9190,6 +9304,44 @@
         <v/>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D59" s="23" t="n">
+        <v>46283</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1985945.49</v>
+      </c>
+      <c r="F59">
+        <f>E59-E58</f>
+        <v/>
+      </c>
+      <c r="G59">
+        <f>F59/E58</f>
+        <v/>
+      </c>
+      <c r="H59" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I59">
+        <f>F59/H59</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2532,17 +2532,17 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2550,21 +2550,21 @@
       <c r="D53" s="23" t="n">
         <v>46283</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" s="3" t="n">
         <v>796026.6800000001</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="3">
         <f>E53-E52</f>
         <v/>
       </c>
-      <c r="G53">
+      <c r="G53" s="3">
         <f>F53/E52</f>
         <v/>
       </c>
-      <c r="H53" t="n">
+      <c r="H53" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I53">
+      <c r="I53" s="3">
         <f>F53/H53</f>
         <v/>
       </c>
@@ -4785,17 +4785,17 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -4803,21 +4803,21 @@
       <c r="D59" s="23" t="n">
         <v>46283</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" s="3" t="n">
         <v>632901.66</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="3">
         <f>E59-E58</f>
         <v/>
       </c>
-      <c r="G59">
+      <c r="G59" s="3">
         <f>F59/E58</f>
         <v/>
       </c>
-      <c r="H59" t="n">
+      <c r="H59" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I59">
+      <c r="I59" s="3">
         <f>F59/H59</f>
         <v/>
       </c>
@@ -6822,17 +6822,17 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -6840,21 +6840,21 @@
       <c r="D53" s="23" t="n">
         <v>46283</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" s="3" t="n">
         <v>2365968.77</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="3">
         <f>E53-E52</f>
         <v/>
       </c>
-      <c r="G53">
+      <c r="G53" s="3">
         <f>F53/E52</f>
         <v/>
       </c>
-      <c r="H53" t="n">
+      <c r="H53" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I53">
+      <c r="I53" s="3">
         <f>F53/H53</f>
         <v/>
       </c>
@@ -9305,17 +9305,17 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -9323,21 +9323,21 @@
       <c r="D59" s="23" t="n">
         <v>46283</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" s="3" t="n">
         <v>1985945.49</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="3">
         <f>E59-E58</f>
         <v/>
       </c>
-      <c r="G59">
+      <c r="G59" s="3">
         <f>F59/E58</f>
         <v/>
       </c>
-      <c r="H59" t="n">
+      <c r="H59" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I59">
+      <c r="I59" s="3">
         <f>F59/H59</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2566,6 +2566,44 @@
       </c>
       <c r="I53" s="3">
         <f>F53/H53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D54" s="23" t="n">
+        <v>46286</v>
+      </c>
+      <c r="E54" t="n">
+        <v>768936.6800000001</v>
+      </c>
+      <c r="F54">
+        <f>E54-E53</f>
+        <v/>
+      </c>
+      <c r="G54">
+        <f>F54/E53</f>
+        <v/>
+      </c>
+      <c r="H54" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I54">
+        <f>F54/H54</f>
         <v/>
       </c>
     </row>
@@ -2580,7 +2618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4819,6 +4857,44 @@
       </c>
       <c r="I59" s="3">
         <f>F59/H59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D60" s="23" t="n">
+        <v>46286</v>
+      </c>
+      <c r="E60" t="n">
+        <v>633171.66</v>
+      </c>
+      <c r="F60">
+        <f>E60-E59</f>
+        <v/>
+      </c>
+      <c r="G60">
+        <f>F60/E59</f>
+        <v/>
+      </c>
+      <c r="H60" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I60">
+        <f>F60/H60</f>
         <v/>
       </c>
     </row>
@@ -4833,7 +4909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -6856,6 +6932,44 @@
       </c>
       <c r="I53" s="3">
         <f>F53/H53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D54" s="23" t="n">
+        <v>46286</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2371368.77</v>
+      </c>
+      <c r="F54">
+        <f>E54-E53</f>
+        <v/>
+      </c>
+      <c r="G54">
+        <f>F54/E53</f>
+        <v/>
+      </c>
+      <c r="H54" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I54">
+        <f>F54/H54</f>
         <v/>
       </c>
     </row>
@@ -6958,11 +7072,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续5日增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-5+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-1+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6999,7 +7113,7 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I3" s="13">
@@ -7040,11 +7154,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续2日减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7081,11 +7195,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续3日减持</t>
+          <t>连续4日减持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-3+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-4+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7100,7 +7214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9342,6 +9456,44 @@
         <v/>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D60" s="23" t="n">
+        <v>46286</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1963045.49</v>
+      </c>
+      <c r="F60">
+        <f>E60-E59</f>
+        <v/>
+      </c>
+      <c r="G60">
+        <f>F60/E59</f>
+        <v/>
+      </c>
+      <c r="H60" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I60">
+        <f>F60/H60</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2570,17 +2570,17 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2588,21 +2588,21 @@
       <c r="D54" s="23" t="n">
         <v>46286</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" s="3" t="n">
         <v>768936.6800000001</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="3">
         <f>E54-E53</f>
         <v/>
       </c>
-      <c r="G54">
+      <c r="G54" s="3">
         <f>F54/E53</f>
         <v/>
       </c>
-      <c r="H54" t="n">
+      <c r="H54" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I54">
+      <c r="I54" s="3">
         <f>F54/H54</f>
         <v/>
       </c>
@@ -4861,17 +4861,17 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -4879,21 +4879,21 @@
       <c r="D60" s="23" t="n">
         <v>46286</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60" s="3" t="n">
         <v>633171.66</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="3">
         <f>E60-E59</f>
         <v/>
       </c>
-      <c r="G60">
+      <c r="G60" s="3">
         <f>F60/E59</f>
         <v/>
       </c>
-      <c r="H60" t="n">
+      <c r="H60" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I60">
+      <c r="I60" s="3">
         <f>F60/H60</f>
         <v/>
       </c>
@@ -6936,17 +6936,17 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -6954,21 +6954,21 @@
       <c r="D54" s="23" t="n">
         <v>46286</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" s="3" t="n">
         <v>2371368.77</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="3">
         <f>E54-E53</f>
         <v/>
       </c>
-      <c r="G54">
+      <c r="G54" s="3">
         <f>F54/E53</f>
         <v/>
       </c>
-      <c r="H54" t="n">
+      <c r="H54" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I54">
+      <c r="I54" s="3">
         <f>F54/H54</f>
         <v/>
       </c>
@@ -9457,17 +9457,17 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -9475,21 +9475,21 @@
       <c r="D60" s="23" t="n">
         <v>46286</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60" s="3" t="n">
         <v>1963045.49</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="3">
         <f>E60-E59</f>
         <v/>
       </c>
-      <c r="G60">
+      <c r="G60" s="3">
         <f>F60/E59</f>
         <v/>
       </c>
-      <c r="H60" t="n">
+      <c r="H60" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I60">
+      <c r="I60" s="3">
         <f>F60/H60</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2604,6 +2604,44 @@
       </c>
       <c r="I54" s="3">
         <f>F54/H54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E55" t="n">
+        <v>747606.6800000001</v>
+      </c>
+      <c r="F55">
+        <f>E55-E54</f>
+        <v/>
+      </c>
+      <c r="G55">
+        <f>F55/E54</f>
+        <v/>
+      </c>
+      <c r="H55" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I55">
+        <f>F55/H55</f>
         <v/>
       </c>
     </row>
@@ -2618,7 +2656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4895,6 +4933,44 @@
       </c>
       <c r="I60" s="3">
         <f>F60/H60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D61" s="23" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E61" t="n">
+        <v>644511.66</v>
+      </c>
+      <c r="F61">
+        <f>E61-E60</f>
+        <v/>
+      </c>
+      <c r="G61">
+        <f>F61/E60</f>
+        <v/>
+      </c>
+      <c r="H61" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I61">
+        <f>F61/H61</f>
         <v/>
       </c>
     </row>
@@ -4909,7 +4985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -6970,6 +7046,44 @@
       </c>
       <c r="I54" s="3">
         <f>F54/H54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2373798.77</v>
+      </c>
+      <c r="F55">
+        <f>E55-E54</f>
+        <v/>
+      </c>
+      <c r="G55">
+        <f>F55/E54</f>
+        <v/>
+      </c>
+      <c r="H55" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I55">
+        <f>F55/H55</f>
         <v/>
       </c>
     </row>
@@ -7072,11 +7186,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>连续2日减持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-1+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-2+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7113,11 +7227,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>连续2日增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-1+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-2+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7154,11 +7268,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>连续2日增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7195,11 +7309,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续4日减持</t>
+          <t>连续5日减持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-4+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-5+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7214,7 +7328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9494,6 +9608,44 @@
         <v/>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D61" s="23" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1962745.49</v>
+      </c>
+      <c r="F61">
+        <f>E61-E60</f>
+        <v/>
+      </c>
+      <c r="G61">
+        <f>F61/E60</f>
+        <v/>
+      </c>
+      <c r="H61" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I61">
+        <f>F61/H61</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2608,17 +2608,17 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2626,21 +2626,21 @@
       <c r="D55" s="23" t="n">
         <v>46287</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="3" t="n">
         <v>747606.6800000001</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="3">
         <f>E55-E54</f>
         <v/>
       </c>
-      <c r="G55">
+      <c r="G55" s="3">
         <f>F55/E54</f>
         <v/>
       </c>
-      <c r="H55" t="n">
+      <c r="H55" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I55">
+      <c r="I55" s="3">
         <f>F55/H55</f>
         <v/>
       </c>
@@ -4937,17 +4937,17 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -4955,21 +4955,21 @@
       <c r="D61" s="23" t="n">
         <v>46287</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" s="3" t="n">
         <v>644511.66</v>
       </c>
-      <c r="F61">
+      <c r="F61" s="3">
         <f>E61-E60</f>
         <v/>
       </c>
-      <c r="G61">
+      <c r="G61" s="3">
         <f>F61/E60</f>
         <v/>
       </c>
-      <c r="H61" t="n">
+      <c r="H61" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I61">
+      <c r="I61" s="3">
         <f>F61/H61</f>
         <v/>
       </c>
@@ -7050,17 +7050,17 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -7068,21 +7068,21 @@
       <c r="D55" s="23" t="n">
         <v>46287</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="3" t="n">
         <v>2373798.77</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="3">
         <f>E55-E54</f>
         <v/>
       </c>
-      <c r="G55">
+      <c r="G55" s="3">
         <f>F55/E54</f>
         <v/>
       </c>
-      <c r="H55" t="n">
+      <c r="H55" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I55">
+      <c r="I55" s="3">
         <f>F55/H55</f>
         <v/>
       </c>
@@ -9609,17 +9609,17 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -9627,21 +9627,21 @@
       <c r="D61" s="23" t="n">
         <v>46287</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" s="3" t="n">
         <v>1962745.49</v>
       </c>
-      <c r="F61">
+      <c r="F61" s="3">
         <f>E61-E60</f>
         <v/>
       </c>
-      <c r="G61">
+      <c r="G61" s="3">
         <f>F61/E60</f>
         <v/>
       </c>
-      <c r="H61" t="n">
+      <c r="H61" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I61">
+      <c r="I61" s="3">
         <f>F61/H61</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2642,6 +2642,44 @@
       </c>
       <c r="I55" s="3">
         <f>F55/H55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D56" s="23" t="n">
+        <v>46288</v>
+      </c>
+      <c r="E56" t="n">
+        <v>737976.6800000001</v>
+      </c>
+      <c r="F56">
+        <f>E56-E55</f>
+        <v/>
+      </c>
+      <c r="G56">
+        <f>F56/E55</f>
+        <v/>
+      </c>
+      <c r="H56" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I56">
+        <f>F56/H56</f>
         <v/>
       </c>
     </row>
@@ -2656,7 +2694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4971,6 +5009,44 @@
       </c>
       <c r="I61" s="3">
         <f>F61/H61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D62" s="23" t="n">
+        <v>46288</v>
+      </c>
+      <c r="E62" t="n">
+        <v>651891.66</v>
+      </c>
+      <c r="F62">
+        <f>E62-E61</f>
+        <v/>
+      </c>
+      <c r="G62">
+        <f>F62/E61</f>
+        <v/>
+      </c>
+      <c r="H62" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I62">
+        <f>F62/H62</f>
         <v/>
       </c>
     </row>
@@ -4985,7 +5061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -7084,6 +7160,44 @@
       </c>
       <c r="I55" s="3">
         <f>F55/H55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D56" s="23" t="n">
+        <v>46288</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2400528.77</v>
+      </c>
+      <c r="F56">
+        <f>E56-E55</f>
+        <v/>
+      </c>
+      <c r="G56">
+        <f>F56/E55</f>
+        <v/>
+      </c>
+      <c r="H56" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I56">
+        <f>F56/H56</f>
         <v/>
       </c>
     </row>
@@ -7186,11 +7300,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续2日减持</t>
+          <t>连续3日减持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-2+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-3+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7227,11 +7341,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续2日增持</t>
+          <t>连续3日增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-2+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-3+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7268,11 +7382,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续2日增持</t>
+          <t>连续3日增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-3+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7309,11 +7423,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续5日减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-5+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-1+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7328,7 +7442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9646,6 +9760,44 @@
         <v/>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D62" s="23" t="n">
+        <v>46288</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1964845.49</v>
+      </c>
+      <c r="F62">
+        <f>E62-E61</f>
+        <v/>
+      </c>
+      <c r="G62">
+        <f>F62/E61</f>
+        <v/>
+      </c>
+      <c r="H62" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I62">
+        <f>F62/H62</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2646,17 +2646,17 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2664,21 +2664,21 @@
       <c r="D56" s="23" t="n">
         <v>46288</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="3" t="n">
         <v>737976.6800000001</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="3">
         <f>E56-E55</f>
         <v/>
       </c>
-      <c r="G56">
+      <c r="G56" s="3">
         <f>F56/E55</f>
         <v/>
       </c>
-      <c r="H56" t="n">
+      <c r="H56" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I56">
+      <c r="I56" s="3">
         <f>F56/H56</f>
         <v/>
       </c>
@@ -5013,17 +5013,17 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -5031,21 +5031,21 @@
       <c r="D62" s="23" t="n">
         <v>46288</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="3" t="n">
         <v>651891.66</v>
       </c>
-      <c r="F62">
+      <c r="F62" s="3">
         <f>E62-E61</f>
         <v/>
       </c>
-      <c r="G62">
+      <c r="G62" s="3">
         <f>F62/E61</f>
         <v/>
       </c>
-      <c r="H62" t="n">
+      <c r="H62" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I62">
+      <c r="I62" s="3">
         <f>F62/H62</f>
         <v/>
       </c>
@@ -7164,17 +7164,17 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -7182,21 +7182,21 @@
       <c r="D56" s="23" t="n">
         <v>46288</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="3" t="n">
         <v>2400528.77</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="3">
         <f>E56-E55</f>
         <v/>
       </c>
-      <c r="G56">
+      <c r="G56" s="3">
         <f>F56/E55</f>
         <v/>
       </c>
-      <c r="H56" t="n">
+      <c r="H56" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I56">
+      <c r="I56" s="3">
         <f>F56/H56</f>
         <v/>
       </c>
@@ -9761,17 +9761,17 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -9779,21 +9779,21 @@
       <c r="D62" s="23" t="n">
         <v>46288</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="3" t="n">
         <v>1964845.49</v>
       </c>
-      <c r="F62">
+      <c r="F62" s="3">
         <f>E62-E61</f>
         <v/>
       </c>
-      <c r="G62">
+      <c r="G62" s="3">
         <f>F62/E61</f>
         <v/>
       </c>
-      <c r="H62" t="n">
+      <c r="H62" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I62">
+      <c r="I62" s="3">
         <f>F62/H62</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2680,6 +2680,44 @@
       </c>
       <c r="I56" s="3">
         <f>F56/H56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D57" s="23" t="n">
+        <v>46289</v>
+      </c>
+      <c r="E57" t="n">
+        <v>716736.6800000001</v>
+      </c>
+      <c r="F57">
+        <f>E57-E56</f>
+        <v/>
+      </c>
+      <c r="G57">
+        <f>F57/E56</f>
+        <v/>
+      </c>
+      <c r="H57" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I57">
+        <f>F57/H57</f>
         <v/>
       </c>
     </row>
@@ -2694,7 +2732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5047,6 +5085,44 @@
       </c>
       <c r="I62" s="3">
         <f>F62/H62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D63" s="23" t="n">
+        <v>46289</v>
+      </c>
+      <c r="E63" t="n">
+        <v>656661.66</v>
+      </c>
+      <c r="F63">
+        <f>E63-E62</f>
+        <v/>
+      </c>
+      <c r="G63">
+        <f>F63/E62</f>
+        <v/>
+      </c>
+      <c r="H63" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I63">
+        <f>F63/H63</f>
         <v/>
       </c>
     </row>
@@ -5061,7 +5137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -7198,6 +7274,44 @@
       </c>
       <c r="I56" s="3">
         <f>F56/H56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D57" s="23" t="n">
+        <v>46289</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2390448.77</v>
+      </c>
+      <c r="F57">
+        <f>E57-E56</f>
+        <v/>
+      </c>
+      <c r="G57">
+        <f>F57/E56</f>
+        <v/>
+      </c>
+      <c r="H57" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I57">
+        <f>F57/H57</f>
         <v/>
       </c>
     </row>
@@ -7300,11 +7414,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续3日减持</t>
+          <t>连续4日减持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-3+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-4+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7341,11 +7455,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续3日增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-3+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-1+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7382,11 +7496,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续3日增持</t>
+          <t>连续4日增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-3+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-4+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7423,11 +7537,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>连续2日增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-1+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-2+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7442,7 +7556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9798,6 +9912,44 @@
         <v/>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D63" s="23" t="n">
+        <v>46289</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1996345.49</v>
+      </c>
+      <c r="F63">
+        <f>E63-E62</f>
+        <v/>
+      </c>
+      <c r="G63">
+        <f>F63/E62</f>
+        <v/>
+      </c>
+      <c r="H63" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I63">
+        <f>F63/H63</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2684,17 +2684,17 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2702,21 +2702,21 @@
       <c r="D57" s="23" t="n">
         <v>46289</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" s="3" t="n">
         <v>716736.6800000001</v>
       </c>
-      <c r="F57">
+      <c r="F57" s="3">
         <f>E57-E56</f>
         <v/>
       </c>
-      <c r="G57">
+      <c r="G57" s="3">
         <f>F57/E56</f>
         <v/>
       </c>
-      <c r="H57" t="n">
+      <c r="H57" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I57">
+      <c r="I57" s="3">
         <f>F57/H57</f>
         <v/>
       </c>
@@ -5089,17 +5089,17 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -5107,21 +5107,21 @@
       <c r="D63" s="23" t="n">
         <v>46289</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" s="3" t="n">
         <v>656661.66</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="3">
         <f>E63-E62</f>
         <v/>
       </c>
-      <c r="G63">
+      <c r="G63" s="3">
         <f>F63/E62</f>
         <v/>
       </c>
-      <c r="H63" t="n">
+      <c r="H63" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I63">
+      <c r="I63" s="3">
         <f>F63/H63</f>
         <v/>
       </c>
@@ -7278,17 +7278,17 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -7296,21 +7296,21 @@
       <c r="D57" s="23" t="n">
         <v>46289</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" s="3" t="n">
         <v>2390448.77</v>
       </c>
-      <c r="F57">
+      <c r="F57" s="3">
         <f>E57-E56</f>
         <v/>
       </c>
-      <c r="G57">
+      <c r="G57" s="3">
         <f>F57/E56</f>
         <v/>
       </c>
-      <c r="H57" t="n">
+      <c r="H57" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I57">
+      <c r="I57" s="3">
         <f>F57/H57</f>
         <v/>
       </c>
@@ -9913,17 +9913,17 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -9931,21 +9931,21 @@
       <c r="D63" s="23" t="n">
         <v>46289</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" s="3" t="n">
         <v>1996345.49</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="3">
         <f>E63-E62</f>
         <v/>
       </c>
-      <c r="G63">
+      <c r="G63" s="3">
         <f>F63/E62</f>
         <v/>
       </c>
-      <c r="H63" t="n">
+      <c r="H63" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I63">
+      <c r="I63" s="3">
         <f>F63/H63</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2718,6 +2718,44 @@
       </c>
       <c r="I57" s="3">
         <f>F57/H57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D58" s="23" t="n">
+        <v>46293</v>
+      </c>
+      <c r="E58" t="n">
+        <v>736356.6800000001</v>
+      </c>
+      <c r="F58">
+        <f>E58-E57</f>
+        <v/>
+      </c>
+      <c r="G58">
+        <f>F58/E57</f>
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I58">
+        <f>F58/H58</f>
         <v/>
       </c>
     </row>
@@ -2732,7 +2770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5123,6 +5161,44 @@
       </c>
       <c r="I63" s="3">
         <f>F63/H63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D64" s="23" t="n">
+        <v>46293</v>
+      </c>
+      <c r="E64" t="n">
+        <v>659901.66</v>
+      </c>
+      <c r="F64">
+        <f>E64-E63</f>
+        <v/>
+      </c>
+      <c r="G64">
+        <f>F64/E63</f>
+        <v/>
+      </c>
+      <c r="H64" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I64">
+        <f>F64/H64</f>
         <v/>
       </c>
     </row>
@@ -5137,7 +5213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -7312,6 +7388,44 @@
       </c>
       <c r="I57" s="3">
         <f>F57/H57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D58" s="23" t="n">
+        <v>46293</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2417808.77</v>
+      </c>
+      <c r="F58">
+        <f>E58-E57</f>
+        <v/>
+      </c>
+      <c r="G58">
+        <f>F58/E57</f>
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I58">
+        <f>F58/H58</f>
         <v/>
       </c>
     </row>
@@ -7414,11 +7528,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续4日减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-4+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-1+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7455,7 +7569,7 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I3" s="13">
@@ -7496,11 +7610,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续4日增持</t>
+          <t>连续5日增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-4+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-5+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7537,11 +7651,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续2日增持</t>
+          <t>连续3日增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-2+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-3+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7556,7 +7670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9950,6 +10064,44 @@
         <v/>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D64" s="23" t="n">
+        <v>46293</v>
+      </c>
+      <c r="E64" t="n">
+        <v>2086445.49</v>
+      </c>
+      <c r="F64">
+        <f>E64-E63</f>
+        <v/>
+      </c>
+      <c r="G64">
+        <f>F64/E63</f>
+        <v/>
+      </c>
+      <c r="H64" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I64">
+        <f>F64/H64</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2722,17 +2722,17 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2740,21 +2740,21 @@
       <c r="D58" s="23" t="n">
         <v>46293</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58" s="3" t="n">
         <v>736356.6800000001</v>
       </c>
-      <c r="F58">
+      <c r="F58" s="3">
         <f>E58-E57</f>
         <v/>
       </c>
-      <c r="G58">
+      <c r="G58" s="3">
         <f>F58/E57</f>
         <v/>
       </c>
-      <c r="H58" t="n">
+      <c r="H58" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I58">
+      <c r="I58" s="3">
         <f>F58/H58</f>
         <v/>
       </c>
@@ -5165,17 +5165,17 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -5183,21 +5183,21 @@
       <c r="D64" s="23" t="n">
         <v>46293</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64" s="3" t="n">
         <v>659901.66</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="3">
         <f>E64-E63</f>
         <v/>
       </c>
-      <c r="G64">
+      <c r="G64" s="3">
         <f>F64/E63</f>
         <v/>
       </c>
-      <c r="H64" t="n">
+      <c r="H64" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I64">
+      <c r="I64" s="3">
         <f>F64/H64</f>
         <v/>
       </c>
@@ -7392,17 +7392,17 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -7410,21 +7410,21 @@
       <c r="D58" s="23" t="n">
         <v>46293</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58" s="3" t="n">
         <v>2417808.77</v>
       </c>
-      <c r="F58">
+      <c r="F58" s="3">
         <f>E58-E57</f>
         <v/>
       </c>
-      <c r="G58">
+      <c r="G58" s="3">
         <f>F58/E57</f>
         <v/>
       </c>
-      <c r="H58" t="n">
+      <c r="H58" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I58">
+      <c r="I58" s="3">
         <f>F58/H58</f>
         <v/>
       </c>
@@ -10065,17 +10065,17 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -10083,21 +10083,21 @@
       <c r="D64" s="23" t="n">
         <v>46293</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64" s="3" t="n">
         <v>2086445.49</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="3">
         <f>E64-E63</f>
         <v/>
       </c>
-      <c r="G64">
+      <c r="G64" s="3">
         <f>F64/E63</f>
         <v/>
       </c>
-      <c r="H64" t="n">
+      <c r="H64" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I64">
+      <c r="I64" s="3">
         <f>F64/H64</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2756,6 +2756,44 @@
       </c>
       <c r="I58" s="3">
         <f>F58/H58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D59" s="23" t="n">
+        <v>46294</v>
+      </c>
+      <c r="E59" t="n">
+        <v>724836.6800000001</v>
+      </c>
+      <c r="F59">
+        <f>E59-E58</f>
+        <v/>
+      </c>
+      <c r="G59">
+        <f>F59/E58</f>
+        <v/>
+      </c>
+      <c r="H59" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I59">
+        <f>F59/H59</f>
         <v/>
       </c>
     </row>
@@ -2770,7 +2808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5199,6 +5237,44 @@
       </c>
       <c r="I64" s="3">
         <f>F64/H64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D65" s="23" t="n">
+        <v>46294</v>
+      </c>
+      <c r="E65" t="n">
+        <v>661881.66</v>
+      </c>
+      <c r="F65">
+        <f>E65-E64</f>
+        <v/>
+      </c>
+      <c r="G65">
+        <f>F65/E64</f>
+        <v/>
+      </c>
+      <c r="H65" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I65">
+        <f>F65/H65</f>
         <v/>
       </c>
     </row>
@@ -5213,7 +5289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -7426,6 +7502,44 @@
       </c>
       <c r="I58" s="3">
         <f>F58/H58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D59" s="23" t="n">
+        <v>46294</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2416458.77</v>
+      </c>
+      <c r="F59">
+        <f>E59-E58</f>
+        <v/>
+      </c>
+      <c r="G59">
+        <f>F59/E58</f>
+        <v/>
+      </c>
+      <c r="H59" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I59">
+        <f>F59/H59</f>
         <v/>
       </c>
     </row>
@@ -7528,7 +7642,7 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I2" s="13">
@@ -7569,7 +7683,7 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I3" s="13">
@@ -7610,11 +7724,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续5日增持</t>
+          <t>连续6日增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-5+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-6+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7651,11 +7765,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续3日增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-3+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-1+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7670,7 +7784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10102,6 +10216,44 @@
         <v/>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D65" s="23" t="n">
+        <v>46294</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2073045.49</v>
+      </c>
+      <c r="F65">
+        <f>E65-E64</f>
+        <v/>
+      </c>
+      <c r="G65">
+        <f>F65/E64</f>
+        <v/>
+      </c>
+      <c r="H65" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I65">
+        <f>F65/H65</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2760,17 +2760,17 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2778,21 +2778,21 @@
       <c r="D59" s="23" t="n">
         <v>46294</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" s="3" t="n">
         <v>724836.6800000001</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="3">
         <f>E59-E58</f>
         <v/>
       </c>
-      <c r="G59">
+      <c r="G59" s="3">
         <f>F59/E58</f>
         <v/>
       </c>
-      <c r="H59" t="n">
+      <c r="H59" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I59">
+      <c r="I59" s="3">
         <f>F59/H59</f>
         <v/>
       </c>
@@ -5241,17 +5241,17 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -5259,21 +5259,21 @@
       <c r="D65" s="23" t="n">
         <v>46294</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" s="3" t="n">
         <v>661881.66</v>
       </c>
-      <c r="F65">
+      <c r="F65" s="3">
         <f>E65-E64</f>
         <v/>
       </c>
-      <c r="G65">
+      <c r="G65" s="3">
         <f>F65/E64</f>
         <v/>
       </c>
-      <c r="H65" t="n">
+      <c r="H65" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I65">
+      <c r="I65" s="3">
         <f>F65/H65</f>
         <v/>
       </c>
@@ -7506,17 +7506,17 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -7524,21 +7524,21 @@
       <c r="D59" s="23" t="n">
         <v>46294</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" s="3" t="n">
         <v>2416458.77</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="3">
         <f>E59-E58</f>
         <v/>
       </c>
-      <c r="G59">
+      <c r="G59" s="3">
         <f>F59/E58</f>
         <v/>
       </c>
-      <c r="H59" t="n">
+      <c r="H59" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I59">
+      <c r="I59" s="3">
         <f>F59/H59</f>
         <v/>
       </c>
@@ -10217,17 +10217,17 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -10235,21 +10235,21 @@
       <c r="D65" s="23" t="n">
         <v>46294</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" s="3" t="n">
         <v>2073045.49</v>
       </c>
-      <c r="F65">
+      <c r="F65" s="3">
         <f>E65-E64</f>
         <v/>
       </c>
-      <c r="G65">
+      <c r="G65" s="3">
         <f>F65/E64</f>
         <v/>
       </c>
-      <c r="H65" t="n">
+      <c r="H65" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I65">
+      <c r="I65" s="3">
         <f>F65/H65</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2808,7 +2808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5275,6 +5275,44 @@
       </c>
       <c r="I65" s="3">
         <f>F65/H65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D66" s="23" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E66" t="n">
+        <v>686631.66</v>
+      </c>
+      <c r="F66">
+        <f>E66-E65</f>
+        <v/>
+      </c>
+      <c r="G66">
+        <f>F66/E65</f>
+        <v/>
+      </c>
+      <c r="H66" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I66">
+        <f>F66/H66</f>
         <v/>
       </c>
     </row>
@@ -7724,11 +7762,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续6日增持</t>
+          <t>连续7日增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-6+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-7+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7765,11 +7803,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>连续2日减持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-1+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-2+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7784,7 +7822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10254,6 +10292,44 @@
         <v/>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D66" s="23" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2060945.49</v>
+      </c>
+      <c r="F66">
+        <f>E66-E65</f>
+        <v/>
+      </c>
+      <c r="G66">
+        <f>F66/E65</f>
+        <v/>
+      </c>
+      <c r="H66" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I66">
+        <f>F66/H66</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2794,6 +2794,44 @@
       </c>
       <c r="I59" s="3">
         <f>F59/H59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D60" s="23" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E60" t="n">
+        <v>693876.6800000001</v>
+      </c>
+      <c r="F60">
+        <f>E60-E59</f>
+        <v/>
+      </c>
+      <c r="G60">
+        <f>F60/E59</f>
+        <v/>
+      </c>
+      <c r="H60" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I60">
+        <f>F60/H60</f>
         <v/>
       </c>
     </row>
@@ -5279,17 +5317,17 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -5297,21 +5335,21 @@
       <c r="D66" s="23" t="n">
         <v>46295</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" s="3" t="n">
         <v>686631.66</v>
       </c>
-      <c r="F66">
+      <c r="F66" s="3">
         <f>E66-E65</f>
         <v/>
       </c>
-      <c r="G66">
+      <c r="G66" s="3">
         <f>F66/E65</f>
         <v/>
       </c>
-      <c r="H66" t="n">
+      <c r="H66" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I66">
+      <c r="I66" s="3">
         <f>F66/H66</f>
         <v/>
       </c>
@@ -5327,7 +5365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -7578,6 +7616,44 @@
       </c>
       <c r="I59" s="3">
         <f>F59/H59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D60" s="23" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2411958.77</v>
+      </c>
+      <c r="F60">
+        <f>E60-E59</f>
+        <v/>
+      </c>
+      <c r="G60">
+        <f>F60/E59</f>
+        <v/>
+      </c>
+      <c r="H60" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I60">
+        <f>F60/H60</f>
         <v/>
       </c>
     </row>
@@ -7680,11 +7756,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>连续2日减持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-1+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-2+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7721,11 +7797,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>连续2日减持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-1+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-2+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -10293,17 +10369,17 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -10311,21 +10387,21 @@
       <c r="D66" s="23" t="n">
         <v>46295</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" s="3" t="n">
         <v>2060945.49</v>
       </c>
-      <c r="F66">
+      <c r="F66" s="3">
         <f>E66-E65</f>
         <v/>
       </c>
-      <c r="G66">
+      <c r="G66" s="3">
         <f>F66/E65</f>
         <v/>
       </c>
-      <c r="H66" t="n">
+      <c r="H66" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I66">
+      <c r="I66" s="3">
         <f>F66/H66</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2798,17 +2798,17 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2816,21 +2816,21 @@
       <c r="D60" s="23" t="n">
         <v>46295</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60" s="3" t="n">
         <v>693876.6800000001</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="3">
         <f>E60-E59</f>
         <v/>
       </c>
-      <c r="G60">
+      <c r="G60" s="3">
         <f>F60/E59</f>
         <v/>
       </c>
-      <c r="H60" t="n">
+      <c r="H60" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I60">
+      <c r="I60" s="3">
         <f>F60/H60</f>
         <v/>
       </c>
@@ -7620,17 +7620,17 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -7638,21 +7638,21 @@
       <c r="D60" s="23" t="n">
         <v>46295</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60" s="3" t="n">
         <v>2411958.77</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="3">
         <f>E60-E59</f>
         <v/>
       </c>
-      <c r="G60">
+      <c r="G60" s="3">
         <f>F60/E59</f>
         <v/>
       </c>
-      <c r="H60" t="n">
+      <c r="H60" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I60">
+      <c r="I60" s="3">
         <f>F60/H60</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2832,6 +2832,44 @@
       </c>
       <c r="I60" s="3">
         <f>F60/H60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D61" s="23" t="n">
+        <v>46303</v>
+      </c>
+      <c r="E61" t="n">
+        <v>693516.6800000001</v>
+      </c>
+      <c r="F61">
+        <f>E61-E60</f>
+        <v/>
+      </c>
+      <c r="G61">
+        <f>F61/E60</f>
+        <v/>
+      </c>
+      <c r="H61" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I61">
+        <f>F61/H61</f>
         <v/>
       </c>
     </row>
@@ -2846,7 +2884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5351,6 +5389,44 @@
       </c>
       <c r="I66" s="3">
         <f>F66/H66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D67" s="23" t="n">
+        <v>46303</v>
+      </c>
+      <c r="E67" t="n">
+        <v>687891.66</v>
+      </c>
+      <c r="F67">
+        <f>E67-E66</f>
+        <v/>
+      </c>
+      <c r="G67">
+        <f>F67/E66</f>
+        <v/>
+      </c>
+      <c r="H67" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I67">
+        <f>F67/H67</f>
         <v/>
       </c>
     </row>
@@ -5365,7 +5441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -7654,6 +7730,44 @@
       </c>
       <c r="I60" s="3">
         <f>F60/H60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D61" s="23" t="n">
+        <v>46303</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2406378.77</v>
+      </c>
+      <c r="F61">
+        <f>E61-E60</f>
+        <v/>
+      </c>
+      <c r="G61">
+        <f>F61/E60</f>
+        <v/>
+      </c>
+      <c r="H61" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I61">
+        <f>F61/H61</f>
         <v/>
       </c>
     </row>
@@ -7756,11 +7870,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续2日减持</t>
+          <t>连续3日减持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-2+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-3+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7797,11 +7911,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续2日减持</t>
+          <t>连续3日减持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-2+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-3+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7838,11 +7952,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续7日增持</t>
+          <t>连续8日增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-7+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-8+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7879,11 +7993,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续2日减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-2+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-1+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7898,7 +8012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10406,6 +10520,44 @@
         <v/>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D67" s="23" t="n">
+        <v>46303</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2130845.49</v>
+      </c>
+      <c r="F67">
+        <f>E67-E66</f>
+        <v/>
+      </c>
+      <c r="G67">
+        <f>F67/E66</f>
+        <v/>
+      </c>
+      <c r="H67" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I67">
+        <f>F67/H67</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2836,17 +2836,17 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2854,21 +2854,21 @@
       <c r="D61" s="23" t="n">
         <v>46303</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" s="3" t="n">
         <v>693516.6800000001</v>
       </c>
-      <c r="F61">
+      <c r="F61" s="3">
         <f>E61-E60</f>
         <v/>
       </c>
-      <c r="G61">
+      <c r="G61" s="3">
         <f>F61/E60</f>
         <v/>
       </c>
-      <c r="H61" t="n">
+      <c r="H61" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I61">
+      <c r="I61" s="3">
         <f>F61/H61</f>
         <v/>
       </c>
@@ -5393,17 +5393,17 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -5411,21 +5411,21 @@
       <c r="D67" s="23" t="n">
         <v>46303</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" s="3" t="n">
         <v>687891.66</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="3">
         <f>E67-E66</f>
         <v/>
       </c>
-      <c r="G67">
+      <c r="G67" s="3">
         <f>F67/E66</f>
         <v/>
       </c>
-      <c r="H67" t="n">
+      <c r="H67" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I67">
+      <c r="I67" s="3">
         <f>F67/H67</f>
         <v/>
       </c>
@@ -7734,17 +7734,17 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -7752,21 +7752,21 @@
       <c r="D61" s="23" t="n">
         <v>46303</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" s="3" t="n">
         <v>2406378.77</v>
       </c>
-      <c r="F61">
+      <c r="F61" s="3">
         <f>E61-E60</f>
         <v/>
       </c>
-      <c r="G61">
+      <c r="G61" s="3">
         <f>F61/E60</f>
         <v/>
       </c>
-      <c r="H61" t="n">
+      <c r="H61" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I61">
+      <c r="I61" s="3">
         <f>F61/H61</f>
         <v/>
       </c>
@@ -10521,17 +10521,17 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -10539,21 +10539,21 @@
       <c r="D67" s="23" t="n">
         <v>46303</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" s="3" t="n">
         <v>2130845.49</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="3">
         <f>E67-E66</f>
         <v/>
       </c>
-      <c r="G67">
+      <c r="G67" s="3">
         <f>F67/E66</f>
         <v/>
       </c>
-      <c r="H67" t="n">
+      <c r="H67" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I67">
+      <c r="I67" s="3">
         <f>F67/H67</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2870,6 +2870,44 @@
       </c>
       <c r="I61" s="3">
         <f>F61/H61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D62" s="23" t="n">
+        <v>46304</v>
+      </c>
+      <c r="E62" t="n">
+        <v>712236.6800000001</v>
+      </c>
+      <c r="F62">
+        <f>E62-E61</f>
+        <v/>
+      </c>
+      <c r="G62">
+        <f>F62/E61</f>
+        <v/>
+      </c>
+      <c r="H62" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I62">
+        <f>F62/H62</f>
         <v/>
       </c>
     </row>
@@ -2884,7 +2922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5427,6 +5465,44 @@
       </c>
       <c r="I67" s="3">
         <f>F67/H67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D68" s="23" t="n">
+        <v>46304</v>
+      </c>
+      <c r="E68" t="n">
+        <v>685641.66</v>
+      </c>
+      <c r="F68">
+        <f>E68-E67</f>
+        <v/>
+      </c>
+      <c r="G68">
+        <f>F68/E67</f>
+        <v/>
+      </c>
+      <c r="H68" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I68">
+        <f>F68/H68</f>
         <v/>
       </c>
     </row>
@@ -5441,7 +5517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -7768,6 +7844,44 @@
       </c>
       <c r="I61" s="3">
         <f>F61/H61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D62" s="23" t="n">
+        <v>46304</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2439228.77</v>
+      </c>
+      <c r="F62">
+        <f>E62-E61</f>
+        <v/>
+      </c>
+      <c r="G62">
+        <f>F62/E61</f>
+        <v/>
+      </c>
+      <c r="H62" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I62">
+        <f>F62/H62</f>
         <v/>
       </c>
     </row>
@@ -7870,11 +7984,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续3日减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-3+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-1+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7911,11 +8025,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续3日减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-3+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-1+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7952,11 +8066,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续8日增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-8+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7993,11 +8107,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>连续2日增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-1+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-2+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8012,7 +8126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10558,6 +10672,44 @@
         <v/>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D68" s="23" t="n">
+        <v>46304</v>
+      </c>
+      <c r="E68" t="n">
+        <v>2202245.49</v>
+      </c>
+      <c r="F68">
+        <f>E68-E67</f>
+        <v/>
+      </c>
+      <c r="G68">
+        <f>F68/E67</f>
+        <v/>
+      </c>
+      <c r="H68" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I68">
+        <f>F68/H68</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2874,17 +2874,17 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2892,21 +2892,21 @@
       <c r="D62" s="23" t="n">
         <v>46304</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="3" t="n">
         <v>712236.6800000001</v>
       </c>
-      <c r="F62">
+      <c r="F62" s="3">
         <f>E62-E61</f>
         <v/>
       </c>
-      <c r="G62">
+      <c r="G62" s="3">
         <f>F62/E61</f>
         <v/>
       </c>
-      <c r="H62" t="n">
+      <c r="H62" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I62">
+      <c r="I62" s="3">
         <f>F62/H62</f>
         <v/>
       </c>
@@ -5469,17 +5469,17 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -5487,21 +5487,21 @@
       <c r="D68" s="23" t="n">
         <v>46304</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68" s="3" t="n">
         <v>685641.66</v>
       </c>
-      <c r="F68">
+      <c r="F68" s="3">
         <f>E68-E67</f>
         <v/>
       </c>
-      <c r="G68">
+      <c r="G68" s="3">
         <f>F68/E67</f>
         <v/>
       </c>
-      <c r="H68" t="n">
+      <c r="H68" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I68">
+      <c r="I68" s="3">
         <f>F68/H68</f>
         <v/>
       </c>
@@ -7848,17 +7848,17 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -7866,21 +7866,21 @@
       <c r="D62" s="23" t="n">
         <v>46304</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="3" t="n">
         <v>2439228.77</v>
       </c>
-      <c r="F62">
+      <c r="F62" s="3">
         <f>E62-E61</f>
         <v/>
       </c>
-      <c r="G62">
+      <c r="G62" s="3">
         <f>F62/E61</f>
         <v/>
       </c>
-      <c r="H62" t="n">
+      <c r="H62" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I62">
+      <c r="I62" s="3">
         <f>F62/H62</f>
         <v/>
       </c>
@@ -10673,17 +10673,17 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -10691,21 +10691,21 @@
       <c r="D68" s="23" t="n">
         <v>46304</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68" s="3" t="n">
         <v>2202245.49</v>
       </c>
-      <c r="F68">
+      <c r="F68" s="3">
         <f>E68-E67</f>
         <v/>
       </c>
-      <c r="G68">
+      <c r="G68" s="3">
         <f>F68/E67</f>
         <v/>
       </c>
-      <c r="H68" t="n">
+      <c r="H68" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I68">
+      <c r="I68" s="3">
         <f>F68/H68</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2908,6 +2908,44 @@
       </c>
       <c r="I62" s="3">
         <f>F62/H62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D63" s="23" t="n">
+        <v>46307</v>
+      </c>
+      <c r="E63" t="n">
+        <v>711966.6800000001</v>
+      </c>
+      <c r="F63">
+        <f>E63-E62</f>
+        <v/>
+      </c>
+      <c r="G63">
+        <f>F63/E62</f>
+        <v/>
+      </c>
+      <c r="H63" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I63">
+        <f>F63/H63</f>
         <v/>
       </c>
     </row>
@@ -2922,7 +2960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5503,6 +5541,44 @@
       </c>
       <c r="I68" s="3">
         <f>F68/H68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D69" s="23" t="n">
+        <v>46307</v>
+      </c>
+      <c r="E69" t="n">
+        <v>684471.66</v>
+      </c>
+      <c r="F69">
+        <f>E69-E68</f>
+        <v/>
+      </c>
+      <c r="G69">
+        <f>F69/E68</f>
+        <v/>
+      </c>
+      <c r="H69" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I69">
+        <f>F69/H69</f>
         <v/>
       </c>
     </row>
@@ -5517,7 +5593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -7882,6 +7958,44 @@
       </c>
       <c r="I62" s="3">
         <f>F62/H62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D63" s="23" t="n">
+        <v>46307</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2452998.77</v>
+      </c>
+      <c r="F63">
+        <f>E63-E62</f>
+        <v/>
+      </c>
+      <c r="G63">
+        <f>F63/E62</f>
+        <v/>
+      </c>
+      <c r="H63" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I63">
+        <f>F63/H63</f>
         <v/>
       </c>
     </row>
@@ -7984,7 +8098,7 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I2" s="13">
@@ -8025,11 +8139,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>连续2日增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-1+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-2+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8066,11 +8180,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>连续2日减持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8107,11 +8221,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续2日增持</t>
+          <t>连续3日增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-2+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-3+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8126,7 +8240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10710,6 +10824,44 @@
         <v/>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D69" s="23" t="n">
+        <v>46307</v>
+      </c>
+      <c r="E69" t="n">
+        <v>2222645.49</v>
+      </c>
+      <c r="F69">
+        <f>E69-E68</f>
+        <v/>
+      </c>
+      <c r="G69">
+        <f>F69/E68</f>
+        <v/>
+      </c>
+      <c r="H69" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I69">
+        <f>F69/H69</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2912,17 +2912,17 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2930,21 +2930,21 @@
       <c r="D63" s="23" t="n">
         <v>46307</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" s="3" t="n">
         <v>711966.6800000001</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="3">
         <f>E63-E62</f>
         <v/>
       </c>
-      <c r="G63">
+      <c r="G63" s="3">
         <f>F63/E62</f>
         <v/>
       </c>
-      <c r="H63" t="n">
+      <c r="H63" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I63">
+      <c r="I63" s="3">
         <f>F63/H63</f>
         <v/>
       </c>
@@ -5545,17 +5545,17 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -5563,21 +5563,21 @@
       <c r="D69" s="23" t="n">
         <v>46307</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="3" t="n">
         <v>684471.66</v>
       </c>
-      <c r="F69">
+      <c r="F69" s="3">
         <f>E69-E68</f>
         <v/>
       </c>
-      <c r="G69">
+      <c r="G69" s="3">
         <f>F69/E68</f>
         <v/>
       </c>
-      <c r="H69" t="n">
+      <c r="H69" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I69">
+      <c r="I69" s="3">
         <f>F69/H69</f>
         <v/>
       </c>
@@ -7962,17 +7962,17 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -7980,21 +7980,21 @@
       <c r="D63" s="23" t="n">
         <v>46307</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" s="3" t="n">
         <v>2452998.77</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="3">
         <f>E63-E62</f>
         <v/>
       </c>
-      <c r="G63">
+      <c r="G63" s="3">
         <f>F63/E62</f>
         <v/>
       </c>
-      <c r="H63" t="n">
+      <c r="H63" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I63">
+      <c r="I63" s="3">
         <f>F63/H63</f>
         <v/>
       </c>
@@ -10825,17 +10825,17 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -10843,21 +10843,21 @@
       <c r="D69" s="23" t="n">
         <v>46307</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="3" t="n">
         <v>2222645.49</v>
       </c>
-      <c r="F69">
+      <c r="F69" s="3">
         <f>E69-E68</f>
         <v/>
       </c>
-      <c r="G69">
+      <c r="G69" s="3">
         <f>F69/E68</f>
         <v/>
       </c>
-      <c r="H69" t="n">
+      <c r="H69" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I69">
+      <c r="I69" s="3">
         <f>F69/H69</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2960,7 +2960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5579,6 +5579,44 @@
       </c>
       <c r="I69" s="3">
         <f>F69/H69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D70" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="E70" t="n">
+        <v>684831.66</v>
+      </c>
+      <c r="F70">
+        <f>E70-E69</f>
+        <v/>
+      </c>
+      <c r="G70">
+        <f>F70/E69</f>
+        <v/>
+      </c>
+      <c r="H70" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I70">
+        <f>F70/H70</f>
         <v/>
       </c>
     </row>
@@ -8180,11 +8218,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续2日减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8221,11 +8259,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续3日增持</t>
+          <t>连续4日增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-3+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-4+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8240,7 +8278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10862,6 +10900,44 @@
         <v/>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D70" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2295945.49</v>
+      </c>
+      <c r="F70">
+        <f>E70-E69</f>
+        <v/>
+      </c>
+      <c r="G70">
+        <f>F70/E69</f>
+        <v/>
+      </c>
+      <c r="H70" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I70">
+        <f>F70/H70</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2946,6 +2946,44 @@
       </c>
       <c r="I63" s="3">
         <f>F63/H63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D64" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="E64" t="n">
+        <v>729876.6800000001</v>
+      </c>
+      <c r="F64">
+        <f>E64-E63</f>
+        <v/>
+      </c>
+      <c r="G64">
+        <f>F64/E63</f>
+        <v/>
+      </c>
+      <c r="H64" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I64">
+        <f>F64/H64</f>
         <v/>
       </c>
     </row>
@@ -5583,17 +5621,17 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -5601,21 +5639,21 @@
       <c r="D70" s="23" t="n">
         <v>46308</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70" s="3" t="n">
         <v>684831.66</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="3">
         <f>E70-E69</f>
         <v/>
       </c>
-      <c r="G70">
+      <c r="G70" s="3">
         <f>F70/E69</f>
         <v/>
       </c>
-      <c r="H70" t="n">
+      <c r="H70" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I70">
+      <c r="I70" s="3">
         <f>F70/H70</f>
         <v/>
       </c>
@@ -5631,7 +5669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -8034,6 +8072,44 @@
       </c>
       <c r="I63" s="3">
         <f>F63/H63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D64" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="E64" t="n">
+        <v>2489718.77</v>
+      </c>
+      <c r="F64">
+        <f>E64-E63</f>
+        <v/>
+      </c>
+      <c r="G64">
+        <f>F64/E63</f>
+        <v/>
+      </c>
+      <c r="H64" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I64">
+        <f>F64/H64</f>
         <v/>
       </c>
     </row>
@@ -8136,7 +8212,7 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I2" s="13">
@@ -8177,11 +8253,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续2日增持</t>
+          <t>连续3日增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-2+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-3+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -10901,17 +10977,17 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -10919,21 +10995,21 @@
       <c r="D70" s="23" t="n">
         <v>46308</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70" s="3" t="n">
         <v>2295945.49</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="3">
         <f>E70-E69</f>
         <v/>
       </c>
-      <c r="G70">
+      <c r="G70" s="3">
         <f>F70/E69</f>
         <v/>
       </c>
-      <c r="H70" t="n">
+      <c r="H70" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I70">
+      <c r="I70" s="3">
         <f>F70/H70</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2950,17 +2950,17 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2968,22 +2968,60 @@
       <c r="D64" s="23" t="n">
         <v>46308</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64" s="3" t="n">
         <v>729876.6800000001</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="3">
         <f>E64-E63</f>
         <v/>
       </c>
-      <c r="G64">
+      <c r="G64" s="3">
         <f>F64/E63</f>
         <v/>
       </c>
-      <c r="H64" t="n">
+      <c r="H64" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I64">
+      <c r="I64" s="3">
         <f>F64/H64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D65" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="E65" t="n">
+        <v>731586.6800000001</v>
+      </c>
+      <c r="F65">
+        <f>E65-E64</f>
+        <v/>
+      </c>
+      <c r="G65">
+        <f>F65/E64</f>
+        <v/>
+      </c>
+      <c r="H65" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I65">
+        <f>F65/H65</f>
         <v/>
       </c>
     </row>
@@ -2998,7 +3036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5655,6 +5693,44 @@
       </c>
       <c r="I70" s="3">
         <f>F70/H70</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D71" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="E71" t="n">
+        <v>683931.66</v>
+      </c>
+      <c r="F71">
+        <f>E71-E70</f>
+        <v/>
+      </c>
+      <c r="G71">
+        <f>F71/E70</f>
+        <v/>
+      </c>
+      <c r="H71" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I71">
+        <f>F71/H71</f>
         <v/>
       </c>
     </row>
@@ -5669,7 +5745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -8076,17 +8152,17 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -8094,22 +8170,60 @@
       <c r="D64" s="23" t="n">
         <v>46308</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64" s="3" t="n">
         <v>2489718.77</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="3">
         <f>E64-E63</f>
         <v/>
       </c>
-      <c r="G64">
+      <c r="G64" s="3">
         <f>F64/E63</f>
         <v/>
       </c>
-      <c r="H64" t="n">
+      <c r="H64" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I64">
+      <c r="I64" s="3">
         <f>F64/H64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D65" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2469018.77</v>
+      </c>
+      <c r="F65">
+        <f>E65-E64</f>
+        <v/>
+      </c>
+      <c r="G65">
+        <f>F65/E64</f>
+        <v/>
+      </c>
+      <c r="H65" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I65">
+        <f>F65/H65</f>
         <v/>
       </c>
     </row>
@@ -8212,11 +8326,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>连续2日增持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-1+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-2+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8253,11 +8367,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续3日增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-3+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-1+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8294,7 +8408,7 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I4" s="13">
@@ -8335,11 +8449,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续4日增持</t>
+          <t>连续5日增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-4+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-5+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8354,7 +8468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11014,6 +11128,44 @@
         <v/>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D71" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="E71" t="n">
+        <v>2349745.49</v>
+      </c>
+      <c r="F71">
+        <f>E71-E70</f>
+        <v/>
+      </c>
+      <c r="G71">
+        <f>F71/E70</f>
+        <v/>
+      </c>
+      <c r="H71" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I71">
+        <f>F71/H71</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2988,17 +2988,17 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -3006,21 +3006,21 @@
       <c r="D65" s="23" t="n">
         <v>46309</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" s="3" t="n">
         <v>731586.6800000001</v>
       </c>
-      <c r="F65">
+      <c r="F65" s="3">
         <f>E65-E64</f>
         <v/>
       </c>
-      <c r="G65">
+      <c r="G65" s="3">
         <f>F65/E64</f>
         <v/>
       </c>
-      <c r="H65" t="n">
+      <c r="H65" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I65">
+      <c r="I65" s="3">
         <f>F65/H65</f>
         <v/>
       </c>
@@ -5697,17 +5697,17 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -5715,21 +5715,21 @@
       <c r="D71" s="23" t="n">
         <v>46309</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" s="3" t="n">
         <v>683931.66</v>
       </c>
-      <c r="F71">
+      <c r="F71" s="3">
         <f>E71-E70</f>
         <v/>
       </c>
-      <c r="G71">
+      <c r="G71" s="3">
         <f>F71/E70</f>
         <v/>
       </c>
-      <c r="H71" t="n">
+      <c r="H71" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I71">
+      <c r="I71" s="3">
         <f>F71/H71</f>
         <v/>
       </c>
@@ -8190,17 +8190,17 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -8208,21 +8208,21 @@
       <c r="D65" s="23" t="n">
         <v>46309</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" s="3" t="n">
         <v>2469018.77</v>
       </c>
-      <c r="F65">
+      <c r="F65" s="3">
         <f>E65-E64</f>
         <v/>
       </c>
-      <c r="G65">
+      <c r="G65" s="3">
         <f>F65/E64</f>
         <v/>
       </c>
-      <c r="H65" t="n">
+      <c r="H65" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I65">
+      <c r="I65" s="3">
         <f>F65/H65</f>
         <v/>
       </c>
@@ -11129,17 +11129,17 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -11147,21 +11147,21 @@
       <c r="D71" s="23" t="n">
         <v>46309</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" s="3" t="n">
         <v>2349745.49</v>
       </c>
-      <c r="F71">
+      <c r="F71" s="3">
         <f>E71-E70</f>
         <v/>
       </c>
-      <c r="G71">
+      <c r="G71" s="3">
         <f>F71/E70</f>
         <v/>
       </c>
-      <c r="H71" t="n">
+      <c r="H71" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I71">
+      <c r="I71" s="3">
         <f>F71/H71</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -3022,6 +3022,44 @@
       </c>
       <c r="I65" s="3">
         <f>F65/H65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D66" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="E66" t="n">
+        <v>760296.6800000001</v>
+      </c>
+      <c r="F66">
+        <f>E66-E65</f>
+        <v/>
+      </c>
+      <c r="G66">
+        <f>F66/E65</f>
+        <v/>
+      </c>
+      <c r="H66" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I66">
+        <f>F66/H66</f>
         <v/>
       </c>
     </row>
@@ -3036,7 +3074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5731,6 +5769,44 @@
       </c>
       <c r="I71" s="3">
         <f>F71/H71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D72" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="E72" t="n">
+        <v>685191.66</v>
+      </c>
+      <c r="F72">
+        <f>E72-E71</f>
+        <v/>
+      </c>
+      <c r="G72">
+        <f>F72/E71</f>
+        <v/>
+      </c>
+      <c r="H72" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I72">
+        <f>F72/H72</f>
         <v/>
       </c>
     </row>
@@ -5745,7 +5821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -8224,6 +8300,44 @@
       </c>
       <c r="I65" s="3">
         <f>F65/H65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D66" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2548488.77</v>
+      </c>
+      <c r="F66">
+        <f>E66-E65</f>
+        <v/>
+      </c>
+      <c r="G66">
+        <f>F66/E65</f>
+        <v/>
+      </c>
+      <c r="H66" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I66">
+        <f>F66/H66</f>
         <v/>
       </c>
     </row>
@@ -8326,11 +8440,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续2日增持</t>
+          <t>连续3日增持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-2+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-3+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8367,7 +8481,7 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I3" s="13">
@@ -8408,7 +8522,7 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I4" s="13">
@@ -8449,11 +8563,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续5日增持</t>
+          <t>连续6日增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-5+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-6+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8468,7 +8582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11166,6 +11280,44 @@
         <v/>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D72" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2547045.49</v>
+      </c>
+      <c r="F72">
+        <f>E72-E71</f>
+        <v/>
+      </c>
+      <c r="G72">
+        <f>F72/E71</f>
+        <v/>
+      </c>
+      <c r="H72" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I72">
+        <f>F72/H72</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -3026,17 +3026,17 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -3044,21 +3044,21 @@
       <c r="D66" s="23" t="n">
         <v>46310</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" s="3" t="n">
         <v>760296.6800000001</v>
       </c>
-      <c r="F66">
+      <c r="F66" s="3">
         <f>E66-E65</f>
         <v/>
       </c>
-      <c r="G66">
+      <c r="G66" s="3">
         <f>F66/E65</f>
         <v/>
       </c>
-      <c r="H66" t="n">
+      <c r="H66" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I66">
+      <c r="I66" s="3">
         <f>F66/H66</f>
         <v/>
       </c>
@@ -5773,17 +5773,17 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -5791,21 +5791,21 @@
       <c r="D72" s="23" t="n">
         <v>46310</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72" s="3" t="n">
         <v>685191.66</v>
       </c>
-      <c r="F72">
+      <c r="F72" s="3">
         <f>E72-E71</f>
         <v/>
       </c>
-      <c r="G72">
+      <c r="G72" s="3">
         <f>F72/E71</f>
         <v/>
       </c>
-      <c r="H72" t="n">
+      <c r="H72" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I72">
+      <c r="I72" s="3">
         <f>F72/H72</f>
         <v/>
       </c>
@@ -8304,17 +8304,17 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -8322,21 +8322,21 @@
       <c r="D66" s="23" t="n">
         <v>46310</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" s="3" t="n">
         <v>2548488.77</v>
       </c>
-      <c r="F66">
+      <c r="F66" s="3">
         <f>E66-E65</f>
         <v/>
       </c>
-      <c r="G66">
+      <c r="G66" s="3">
         <f>F66/E65</f>
         <v/>
       </c>
-      <c r="H66" t="n">
+      <c r="H66" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I66">
+      <c r="I66" s="3">
         <f>F66/H66</f>
         <v/>
       </c>
@@ -11281,17 +11281,17 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -11299,21 +11299,21 @@
       <c r="D72" s="23" t="n">
         <v>46310</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72" s="3" t="n">
         <v>2547045.49</v>
       </c>
-      <c r="F72">
+      <c r="F72" s="3">
         <f>E72-E71</f>
         <v/>
       </c>
-      <c r="G72">
+      <c r="G72" s="3">
         <f>F72/E71</f>
         <v/>
       </c>
-      <c r="H72" t="n">
+      <c r="H72" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I72">
+      <c r="I72" s="3">
         <f>F72/H72</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -3060,6 +3060,44 @@
       </c>
       <c r="I66" s="3">
         <f>F66/H66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D67" s="23" t="n">
+        <v>46311</v>
+      </c>
+      <c r="E67" t="n">
+        <v>891606.6800000001</v>
+      </c>
+      <c r="F67">
+        <f>E67-E66</f>
+        <v/>
+      </c>
+      <c r="G67">
+        <f>F67/E66</f>
+        <v/>
+      </c>
+      <c r="H67" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I67">
+        <f>F67/H67</f>
         <v/>
       </c>
     </row>
@@ -3074,7 +3112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5807,6 +5845,44 @@
       </c>
       <c r="I72" s="3">
         <f>F72/H72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D73" s="23" t="n">
+        <v>46311</v>
+      </c>
+      <c r="E73" t="n">
+        <v>692931.66</v>
+      </c>
+      <c r="F73">
+        <f>E73-E72</f>
+        <v/>
+      </c>
+      <c r="G73">
+        <f>F73/E72</f>
+        <v/>
+      </c>
+      <c r="H73" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I73">
+        <f>F73/H73</f>
         <v/>
       </c>
     </row>
@@ -5821,7 +5897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -8338,6 +8414,44 @@
       </c>
       <c r="I66" s="3">
         <f>F66/H66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D67" s="23" t="n">
+        <v>46311</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2855298.77</v>
+      </c>
+      <c r="F67">
+        <f>E67-E66</f>
+        <v/>
+      </c>
+      <c r="G67">
+        <f>F67/E66</f>
+        <v/>
+      </c>
+      <c r="H67" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I67">
+        <f>F67/H67</f>
         <v/>
       </c>
     </row>
@@ -8440,11 +8554,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续3日增持</t>
+          <t>连续4日增持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-3+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-4+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8481,11 +8595,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>连续2日增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-1+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-2+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8522,11 +8636,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>连续2日增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8563,11 +8677,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续6日增持</t>
+          <t>连续7日增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-6+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-7+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8582,7 +8696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11318,6 +11432,44 @@
         <v/>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D73" s="23" t="n">
+        <v>46311</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2593645.49</v>
+      </c>
+      <c r="F73">
+        <f>E73-E72</f>
+        <v/>
+      </c>
+      <c r="G73">
+        <f>F73/E72</f>
+        <v/>
+      </c>
+      <c r="H73" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I73">
+        <f>F73/H73</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -3064,17 +3064,17 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -3082,21 +3082,21 @@
       <c r="D67" s="23" t="n">
         <v>46311</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" s="3" t="n">
         <v>891606.6800000001</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="3">
         <f>E67-E66</f>
         <v/>
       </c>
-      <c r="G67">
+      <c r="G67" s="3">
         <f>F67/E66</f>
         <v/>
       </c>
-      <c r="H67" t="n">
+      <c r="H67" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I67">
+      <c r="I67" s="3">
         <f>F67/H67</f>
         <v/>
       </c>
@@ -5849,17 +5849,17 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -5867,21 +5867,21 @@
       <c r="D73" s="23" t="n">
         <v>46311</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" s="3" t="n">
         <v>692931.66</v>
       </c>
-      <c r="F73">
+      <c r="F73" s="3">
         <f>E73-E72</f>
         <v/>
       </c>
-      <c r="G73">
+      <c r="G73" s="3">
         <f>F73/E72</f>
         <v/>
       </c>
-      <c r="H73" t="n">
+      <c r="H73" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I73">
+      <c r="I73" s="3">
         <f>F73/H73</f>
         <v/>
       </c>
@@ -8418,17 +8418,17 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -8436,21 +8436,21 @@
       <c r="D67" s="23" t="n">
         <v>46311</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" s="3" t="n">
         <v>2855298.77</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="3">
         <f>E67-E66</f>
         <v/>
       </c>
-      <c r="G67">
+      <c r="G67" s="3">
         <f>F67/E66</f>
         <v/>
       </c>
-      <c r="H67" t="n">
+      <c r="H67" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I67">
+      <c r="I67" s="3">
         <f>F67/H67</f>
         <v/>
       </c>
@@ -11433,17 +11433,17 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -11451,21 +11451,21 @@
       <c r="D73" s="23" t="n">
         <v>46311</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" s="3" t="n">
         <v>2593645.49</v>
       </c>
-      <c r="F73">
+      <c r="F73" s="3">
         <f>E73-E72</f>
         <v/>
       </c>
-      <c r="G73">
+      <c r="G73" s="3">
         <f>F73/E72</f>
         <v/>
       </c>
-      <c r="H73" t="n">
+      <c r="H73" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I73">
+      <c r="I73" s="3">
         <f>F73/H73</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -3098,6 +3098,44 @@
       </c>
       <c r="I67" s="3">
         <f>F67/H67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D68" s="23" t="n">
+        <v>46314</v>
+      </c>
+      <c r="E68" t="n">
+        <v>961986.6800000001</v>
+      </c>
+      <c r="F68">
+        <f>E68-E67</f>
+        <v/>
+      </c>
+      <c r="G68">
+        <f>F68/E67</f>
+        <v/>
+      </c>
+      <c r="H68" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I68">
+        <f>F68/H68</f>
         <v/>
       </c>
     </row>
@@ -3112,7 +3150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5883,6 +5921,44 @@
       </c>
       <c r="I73" s="3">
         <f>F73/H73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D74" s="23" t="n">
+        <v>46314</v>
+      </c>
+      <c r="E74" t="n">
+        <v>698601.66</v>
+      </c>
+      <c r="F74">
+        <f>E74-E73</f>
+        <v/>
+      </c>
+      <c r="G74">
+        <f>F74/E73</f>
+        <v/>
+      </c>
+      <c r="H74" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I74">
+        <f>F74/H74</f>
         <v/>
       </c>
     </row>
@@ -5897,7 +5973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -8452,6 +8528,44 @@
       </c>
       <c r="I67" s="3">
         <f>F67/H67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D68" s="23" t="n">
+        <v>46314</v>
+      </c>
+      <c r="E68" t="n">
+        <v>2919558.77</v>
+      </c>
+      <c r="F68">
+        <f>E68-E67</f>
+        <v/>
+      </c>
+      <c r="G68">
+        <f>F68/E67</f>
+        <v/>
+      </c>
+      <c r="H68" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I68">
+        <f>F68/H68</f>
         <v/>
       </c>
     </row>
@@ -8554,11 +8668,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续4日增持</t>
+          <t>连续5日增持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-4+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-5+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8595,11 +8709,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续2日增持</t>
+          <t>连续3日增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-2+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-3+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8636,11 +8750,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续2日增持</t>
+          <t>连续3日增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-3+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8677,11 +8791,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续7日增持</t>
+          <t>连续8日增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-7+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-8+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8696,7 +8810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11470,6 +11584,44 @@
         <v/>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D74" s="23" t="n">
+        <v>46314</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2673645.49</v>
+      </c>
+      <c r="F74">
+        <f>E74-E73</f>
+        <v/>
+      </c>
+      <c r="G74">
+        <f>F74/E73</f>
+        <v/>
+      </c>
+      <c r="H74" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I74">
+        <f>F74/H74</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -3102,17 +3102,17 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -3120,21 +3120,21 @@
       <c r="D68" s="23" t="n">
         <v>46314</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68" s="3" t="n">
         <v>961986.6800000001</v>
       </c>
-      <c r="F68">
+      <c r="F68" s="3">
         <f>E68-E67</f>
         <v/>
       </c>
-      <c r="G68">
+      <c r="G68" s="3">
         <f>F68/E67</f>
         <v/>
       </c>
-      <c r="H68" t="n">
+      <c r="H68" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I68">
+      <c r="I68" s="3">
         <f>F68/H68</f>
         <v/>
       </c>
@@ -5925,17 +5925,17 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -5943,21 +5943,21 @@
       <c r="D74" s="23" t="n">
         <v>46314</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74" s="3" t="n">
         <v>698601.66</v>
       </c>
-      <c r="F74">
+      <c r="F74" s="3">
         <f>E74-E73</f>
         <v/>
       </c>
-      <c r="G74">
+      <c r="G74" s="3">
         <f>F74/E73</f>
         <v/>
       </c>
-      <c r="H74" t="n">
+      <c r="H74" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I74">
+      <c r="I74" s="3">
         <f>F74/H74</f>
         <v/>
       </c>
@@ -8532,17 +8532,17 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -8550,21 +8550,21 @@
       <c r="D68" s="23" t="n">
         <v>46314</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68" s="3" t="n">
         <v>2919558.77</v>
       </c>
-      <c r="F68">
+      <c r="F68" s="3">
         <f>E68-E67</f>
         <v/>
       </c>
-      <c r="G68">
+      <c r="G68" s="3">
         <f>F68/E67</f>
         <v/>
       </c>
-      <c r="H68" t="n">
+      <c r="H68" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I68">
+      <c r="I68" s="3">
         <f>F68/H68</f>
         <v/>
       </c>
@@ -11585,17 +11585,17 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -11603,21 +11603,21 @@
       <c r="D74" s="23" t="n">
         <v>46314</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74" s="3" t="n">
         <v>2673645.49</v>
       </c>
-      <c r="F74">
+      <c r="F74" s="3">
         <f>E74-E73</f>
         <v/>
       </c>
-      <c r="G74">
+      <c r="G74" s="3">
         <f>F74/E73</f>
         <v/>
       </c>
-      <c r="H74" t="n">
+      <c r="H74" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I74">
+      <c r="I74" s="3">
         <f>F74/H74</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -3136,6 +3136,44 @@
       </c>
       <c r="I68" s="3">
         <f>F68/H68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D69" s="23" t="n">
+        <v>46315</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1116066.68</v>
+      </c>
+      <c r="F69">
+        <f>E69-E68</f>
+        <v/>
+      </c>
+      <c r="G69">
+        <f>F69/E68</f>
+        <v/>
+      </c>
+      <c r="H69" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I69">
+        <f>F69/H69</f>
         <v/>
       </c>
     </row>
@@ -3150,7 +3188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5959,6 +5997,44 @@
       </c>
       <c r="I74" s="3">
         <f>F74/H74</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D75" s="23" t="n">
+        <v>46315</v>
+      </c>
+      <c r="E75" t="n">
+        <v>734241.66</v>
+      </c>
+      <c r="F75">
+        <f>E75-E74</f>
+        <v/>
+      </c>
+      <c r="G75">
+        <f>F75/E74</f>
+        <v/>
+      </c>
+      <c r="H75" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I75">
+        <f>F75/H75</f>
         <v/>
       </c>
     </row>
@@ -5973,7 +6049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -8566,6 +8642,44 @@
       </c>
       <c r="I68" s="3">
         <f>F68/H68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D69" s="23" t="n">
+        <v>46315</v>
+      </c>
+      <c r="E69" t="n">
+        <v>2940078.77</v>
+      </c>
+      <c r="F69">
+        <f>E69-E68</f>
+        <v/>
+      </c>
+      <c r="G69">
+        <f>F69/E68</f>
+        <v/>
+      </c>
+      <c r="H69" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I69">
+        <f>F69/H69</f>
         <v/>
       </c>
     </row>
@@ -8668,11 +8782,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续5日增持</t>
+          <t>连续6日增持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-5+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-6+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8709,11 +8823,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续3日增持</t>
+          <t>连续4日增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-3+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-4+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8750,11 +8864,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续3日增持</t>
+          <t>连续4日增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-3+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-4+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8791,11 +8905,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续8日增持</t>
+          <t>连续9日增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-8+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-9+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8810,7 +8924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11622,6 +11736,44 @@
         <v/>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D75" s="23" t="n">
+        <v>46315</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2734345.49</v>
+      </c>
+      <c r="F75">
+        <f>E75-E74</f>
+        <v/>
+      </c>
+      <c r="G75">
+        <f>F75/E74</f>
+        <v/>
+      </c>
+      <c r="H75" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I75">
+        <f>F75/H75</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -3140,17 +3140,17 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -3158,21 +3158,21 @@
       <c r="D69" s="23" t="n">
         <v>46315</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="3" t="n">
         <v>1116066.68</v>
       </c>
-      <c r="F69">
+      <c r="F69" s="3">
         <f>E69-E68</f>
         <v/>
       </c>
-      <c r="G69">
+      <c r="G69" s="3">
         <f>F69/E68</f>
         <v/>
       </c>
-      <c r="H69" t="n">
+      <c r="H69" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I69">
+      <c r="I69" s="3">
         <f>F69/H69</f>
         <v/>
       </c>
@@ -6001,17 +6001,17 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -6019,21 +6019,21 @@
       <c r="D75" s="23" t="n">
         <v>46315</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="3" t="n">
         <v>734241.66</v>
       </c>
-      <c r="F75">
+      <c r="F75" s="3">
         <f>E75-E74</f>
         <v/>
       </c>
-      <c r="G75">
+      <c r="G75" s="3">
         <f>F75/E74</f>
         <v/>
       </c>
-      <c r="H75" t="n">
+      <c r="H75" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I75">
+      <c r="I75" s="3">
         <f>F75/H75</f>
         <v/>
       </c>
@@ -8646,17 +8646,17 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -8664,21 +8664,21 @@
       <c r="D69" s="23" t="n">
         <v>46315</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="3" t="n">
         <v>2940078.77</v>
       </c>
-      <c r="F69">
+      <c r="F69" s="3">
         <f>E69-E68</f>
         <v/>
       </c>
-      <c r="G69">
+      <c r="G69" s="3">
         <f>F69/E68</f>
         <v/>
       </c>
-      <c r="H69" t="n">
+      <c r="H69" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I69">
+      <c r="I69" s="3">
         <f>F69/H69</f>
         <v/>
       </c>
@@ -11737,17 +11737,17 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -11755,21 +11755,21 @@
       <c r="D75" s="23" t="n">
         <v>46315</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="3" t="n">
         <v>2734345.49</v>
       </c>
-      <c r="F75">
+      <c r="F75" s="3">
         <f>E75-E74</f>
         <v/>
       </c>
-      <c r="G75">
+      <c r="G75" s="3">
         <f>F75/E74</f>
         <v/>
       </c>
-      <c r="H75" t="n">
+      <c r="H75" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I75">
+      <c r="I75" s="3">
         <f>F75/H75</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -3174,6 +3174,44 @@
       </c>
       <c r="I69" s="3">
         <f>F69/H69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D70" s="23" t="n">
+        <v>46316</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1139016.68</v>
+      </c>
+      <c r="F70">
+        <f>E70-E69</f>
+        <v/>
+      </c>
+      <c r="G70">
+        <f>F70/E69</f>
+        <v/>
+      </c>
+      <c r="H70" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I70">
+        <f>F70/H70</f>
         <v/>
       </c>
     </row>
@@ -3188,7 +3226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6035,6 +6073,44 @@
       </c>
       <c r="I75" s="3">
         <f>F75/H75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D76" s="23" t="n">
+        <v>46316</v>
+      </c>
+      <c r="E76" t="n">
+        <v>756561.66</v>
+      </c>
+      <c r="F76">
+        <f>E76-E75</f>
+        <v/>
+      </c>
+      <c r="G76">
+        <f>F76/E75</f>
+        <v/>
+      </c>
+      <c r="H76" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I76">
+        <f>F76/H76</f>
         <v/>
       </c>
     </row>
@@ -6049,7 +6125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -8680,6 +8756,44 @@
       </c>
       <c r="I69" s="3">
         <f>F69/H69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D70" s="23" t="n">
+        <v>46316</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3019908.77</v>
+      </c>
+      <c r="F70">
+        <f>E70-E69</f>
+        <v/>
+      </c>
+      <c r="G70">
+        <f>F70/E69</f>
+        <v/>
+      </c>
+      <c r="H70" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I70">
+        <f>F70/H70</f>
         <v/>
       </c>
     </row>
@@ -8782,11 +8896,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续6日增持</t>
+          <t>连续7日增持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-6+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-7+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8823,11 +8937,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续4日增持</t>
+          <t>连续5日增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-4+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-5+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8864,11 +8978,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续4日增持</t>
+          <t>连续5日增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-4+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-5+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8905,11 +9019,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续9日增持</t>
+          <t>连续10日增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-9+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-10+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -8924,7 +9038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11774,6 +11888,44 @@
         <v/>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D76" s="23" t="n">
+        <v>46316</v>
+      </c>
+      <c r="E76" t="n">
+        <v>2920445.49</v>
+      </c>
+      <c r="F76">
+        <f>E76-E75</f>
+        <v/>
+      </c>
+      <c r="G76">
+        <f>F76/E75</f>
+        <v/>
+      </c>
+      <c r="H76" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I76">
+        <f>F76/H76</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -3178,17 +3178,17 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -3196,21 +3196,21 @@
       <c r="D70" s="23" t="n">
         <v>46316</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70" s="3" t="n">
         <v>1139016.68</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="3">
         <f>E70-E69</f>
         <v/>
       </c>
-      <c r="G70">
+      <c r="G70" s="3">
         <f>F70/E69</f>
         <v/>
       </c>
-      <c r="H70" t="n">
+      <c r="H70" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I70">
+      <c r="I70" s="3">
         <f>F70/H70</f>
         <v/>
       </c>
@@ -6077,17 +6077,17 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -6095,21 +6095,21 @@
       <c r="D76" s="23" t="n">
         <v>46316</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76" s="3" t="n">
         <v>756561.66</v>
       </c>
-      <c r="F76">
+      <c r="F76" s="3">
         <f>E76-E75</f>
         <v/>
       </c>
-      <c r="G76">
+      <c r="G76" s="3">
         <f>F76/E75</f>
         <v/>
       </c>
-      <c r="H76" t="n">
+      <c r="H76" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I76">
+      <c r="I76" s="3">
         <f>F76/H76</f>
         <v/>
       </c>
@@ -8760,17 +8760,17 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -8778,21 +8778,21 @@
       <c r="D70" s="23" t="n">
         <v>46316</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70" s="3" t="n">
         <v>3019908.77</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="3">
         <f>E70-E69</f>
         <v/>
       </c>
-      <c r="G70">
+      <c r="G70" s="3">
         <f>F70/E69</f>
         <v/>
       </c>
-      <c r="H70" t="n">
+      <c r="H70" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I70">
+      <c r="I70" s="3">
         <f>F70/H70</f>
         <v/>
       </c>
@@ -11889,17 +11889,17 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -11907,21 +11907,21 @@
       <c r="D76" s="23" t="n">
         <v>46316</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76" s="3" t="n">
         <v>2920445.49</v>
       </c>
-      <c r="F76">
+      <c r="F76" s="3">
         <f>E76-E75</f>
         <v/>
       </c>
-      <c r="G76">
+      <c r="G76" s="3">
         <f>F76/E75</f>
         <v/>
       </c>
-      <c r="H76" t="n">
+      <c r="H76" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I76">
+      <c r="I76" s="3">
         <f>F76/H76</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -3226,7 +3226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6111,6 +6111,44 @@
       </c>
       <c r="I76" s="3">
         <f>F76/H76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D77" s="23" t="n">
+        <v>46317</v>
+      </c>
+      <c r="E77" t="n">
+        <v>976791.66</v>
+      </c>
+      <c r="F77">
+        <f>E77-E76</f>
+        <v/>
+      </c>
+      <c r="G77">
+        <f>F77/E76</f>
+        <v/>
+      </c>
+      <c r="H77" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I77">
+        <f>F77/H77</f>
         <v/>
       </c>
     </row>
@@ -8978,11 +9016,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续5日增持</t>
+          <t>连续6日增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-5+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-6+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -9019,11 +9057,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续10日增持</t>
+          <t>连续11日增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-10+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-11+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -9038,7 +9076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11926,6 +11964,44 @@
         <v/>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D77" s="23" t="n">
+        <v>46317</v>
+      </c>
+      <c r="E77" t="n">
+        <v>3130545.49</v>
+      </c>
+      <c r="F77">
+        <f>E77-E76</f>
+        <v/>
+      </c>
+      <c r="G77">
+        <f>F77/E76</f>
+        <v/>
+      </c>
+      <c r="H77" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I77">
+        <f>F77/H77</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -6115,17 +6115,17 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -6133,21 +6133,21 @@
       <c r="D77" s="23" t="n">
         <v>46317</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77" s="3" t="n">
         <v>976791.66</v>
       </c>
-      <c r="F77">
+      <c r="F77" s="3">
         <f>E77-E76</f>
         <v/>
       </c>
-      <c r="G77">
+      <c r="G77" s="3">
         <f>F77/E76</f>
         <v/>
       </c>
-      <c r="H77" t="n">
+      <c r="H77" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I77">
+      <c r="I77" s="3">
         <f>F77/H77</f>
         <v/>
       </c>
@@ -6163,7 +6163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -8832,6 +8832,44 @@
       </c>
       <c r="I70" s="3">
         <f>F70/H70</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D71" s="23" t="n">
+        <v>46317</v>
+      </c>
+      <c r="E71" t="n">
+        <v>3272988.77</v>
+      </c>
+      <c r="F71">
+        <f>E71-E70</f>
+        <v/>
+      </c>
+      <c r="G71">
+        <f>F71/E70</f>
+        <v/>
+      </c>
+      <c r="H71" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I71">
+        <f>F71/H71</f>
         <v/>
       </c>
     </row>
@@ -8975,11 +9013,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续5日增持</t>
+          <t>连续6日增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-5+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-6+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -11965,17 +12003,17 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -11983,21 +12021,21 @@
       <c r="D77" s="23" t="n">
         <v>46317</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77" s="3" t="n">
         <v>3130545.49</v>
       </c>
-      <c r="F77">
+      <c r="F77" s="3">
         <f>E77-E76</f>
         <v/>
       </c>
-      <c r="G77">
+      <c r="G77" s="3">
         <f>F77/E76</f>
         <v/>
       </c>
-      <c r="H77" t="n">
+      <c r="H77" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I77">
+      <c r="I77" s="3">
         <f>F77/H77</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -3212,6 +3212,44 @@
       </c>
       <c r="I70" s="3">
         <f>F70/H70</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D71" s="23" t="n">
+        <v>46318</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1299306.68</v>
+      </c>
+      <c r="F71">
+        <f>E71-E70</f>
+        <v/>
+      </c>
+      <c r="G71">
+        <f>F71/E70</f>
+        <v/>
+      </c>
+      <c r="H71" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I71">
+        <f>F71/H71</f>
         <v/>
       </c>
     </row>
@@ -3226,7 +3264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6149,6 +6187,44 @@
       </c>
       <c r="I77" s="3">
         <f>F77/H77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D78" s="23" t="n">
+        <v>46318</v>
+      </c>
+      <c r="E78" t="n">
+        <v>998751.66</v>
+      </c>
+      <c r="F78">
+        <f>E78-E77</f>
+        <v/>
+      </c>
+      <c r="G78">
+        <f>F78/E77</f>
+        <v/>
+      </c>
+      <c r="H78" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I78">
+        <f>F78/H78</f>
         <v/>
       </c>
     </row>
@@ -6163,7 +6239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -8836,17 +8912,17 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -8854,22 +8930,60 @@
       <c r="D71" s="23" t="n">
         <v>46317</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" s="3" t="n">
         <v>3272988.77</v>
       </c>
-      <c r="F71">
+      <c r="F71" s="3">
         <f>E71-E70</f>
         <v/>
       </c>
-      <c r="G71">
+      <c r="G71" s="3">
         <f>F71/E70</f>
         <v/>
       </c>
-      <c r="H71" t="n">
+      <c r="H71" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I71">
+      <c r="I71" s="3">
         <f>F71/H71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D72" s="23" t="n">
+        <v>46318</v>
+      </c>
+      <c r="E72" t="n">
+        <v>3524268.77</v>
+      </c>
+      <c r="F72">
+        <f>E72-E71</f>
+        <v/>
+      </c>
+      <c r="G72">
+        <f>F72/E71</f>
+        <v/>
+      </c>
+      <c r="H72" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I72">
+        <f>F72/H72</f>
         <v/>
       </c>
     </row>
@@ -8972,11 +9086,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续7日增持</t>
+          <t>连续8日增持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-7+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-8+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -9013,11 +9127,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续6日增持</t>
+          <t>连续7日增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-6+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-7+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -9054,11 +9168,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续6日增持</t>
+          <t>连续7日增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-6+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-7+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -9095,11 +9209,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续11日增持</t>
+          <t>连续12日增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-11+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-12+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -9114,7 +9228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12040,6 +12154,44 @@
         <v/>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D78" s="23" t="n">
+        <v>46318</v>
+      </c>
+      <c r="E78" t="n">
+        <v>3375745.49</v>
+      </c>
+      <c r="F78">
+        <f>E78-E77</f>
+        <v/>
+      </c>
+      <c r="G78">
+        <f>F78/E77</f>
+        <v/>
+      </c>
+      <c r="H78" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I78">
+        <f>F78/H78</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -3216,17 +3216,17 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -3234,21 +3234,21 @@
       <c r="D71" s="23" t="n">
         <v>46318</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" s="3" t="n">
         <v>1299306.68</v>
       </c>
-      <c r="F71">
+      <c r="F71" s="3">
         <f>E71-E70</f>
         <v/>
       </c>
-      <c r="G71">
+      <c r="G71" s="3">
         <f>F71/E70</f>
         <v/>
       </c>
-      <c r="H71" t="n">
+      <c r="H71" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I71">
+      <c r="I71" s="3">
         <f>F71/H71</f>
         <v/>
       </c>
@@ -6191,17 +6191,17 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -6209,21 +6209,21 @@
       <c r="D78" s="23" t="n">
         <v>46318</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E78" s="3" t="n">
         <v>998751.66</v>
       </c>
-      <c r="F78">
+      <c r="F78" s="3">
         <f>E78-E77</f>
         <v/>
       </c>
-      <c r="G78">
+      <c r="G78" s="3">
         <f>F78/E77</f>
         <v/>
       </c>
-      <c r="H78" t="n">
+      <c r="H78" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I78">
+      <c r="I78" s="3">
         <f>F78/H78</f>
         <v/>
       </c>
@@ -8950,17 +8950,17 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -8968,21 +8968,21 @@
       <c r="D72" s="23" t="n">
         <v>46318</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72" s="3" t="n">
         <v>3524268.77</v>
       </c>
-      <c r="F72">
+      <c r="F72" s="3">
         <f>E72-E71</f>
         <v/>
       </c>
-      <c r="G72">
+      <c r="G72" s="3">
         <f>F72/E71</f>
         <v/>
       </c>
-      <c r="H72" t="n">
+      <c r="H72" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I72">
+      <c r="I72" s="3">
         <f>F72/H72</f>
         <v/>
       </c>
@@ -12155,17 +12155,17 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -12173,21 +12173,21 @@
       <c r="D78" s="23" t="n">
         <v>46318</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E78" s="3" t="n">
         <v>3375745.49</v>
       </c>
-      <c r="F78">
+      <c r="F78" s="3">
         <f>E78-E77</f>
         <v/>
       </c>
-      <c r="G78">
+      <c r="G78" s="3">
         <f>F78/E77</f>
         <v/>
       </c>
-      <c r="H78" t="n">
+      <c r="H78" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I78">
+      <c r="I78" s="3">
         <f>F78/H78</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -3250,6 +3250,44 @@
       </c>
       <c r="I71" s="3">
         <f>F71/H71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D72" s="23" t="n">
+        <v>46321</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1265736.68</v>
+      </c>
+      <c r="F72">
+        <f>E72-E71</f>
+        <v/>
+      </c>
+      <c r="G72">
+        <f>F72/E71</f>
+        <v/>
+      </c>
+      <c r="H72" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I72">
+        <f>F72/H72</f>
         <v/>
       </c>
     </row>
@@ -3264,7 +3302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6225,6 +6263,44 @@
       </c>
       <c r="I78" s="3">
         <f>F78/H78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D79" s="23" t="n">
+        <v>46321</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1040601.66</v>
+      </c>
+      <c r="F79">
+        <f>E79-E78</f>
+        <v/>
+      </c>
+      <c r="G79">
+        <f>F79/E78</f>
+        <v/>
+      </c>
+      <c r="H79" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I79">
+        <f>F79/H79</f>
         <v/>
       </c>
     </row>
@@ -6239,7 +6315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -8984,6 +9060,44 @@
       </c>
       <c r="I72" s="3">
         <f>F72/H72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D73" s="23" t="n">
+        <v>46321</v>
+      </c>
+      <c r="E73" t="n">
+        <v>3544698.77</v>
+      </c>
+      <c r="F73">
+        <f>E73-E72</f>
+        <v/>
+      </c>
+      <c r="G73">
+        <f>F73/E72</f>
+        <v/>
+      </c>
+      <c r="H73" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I73">
+        <f>F73/H73</f>
         <v/>
       </c>
     </row>
@@ -9086,11 +9200,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续8日增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-8+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-1+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -9127,11 +9241,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续7日增持</t>
+          <t>连续8日增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-7+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-8+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -9168,11 +9282,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续7日增持</t>
+          <t>连续8日增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-7+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-8+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -9209,11 +9323,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续12日增持</t>
+          <t>连续13日增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-12+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-13+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -9228,7 +9342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12192,6 +12306,44 @@
         <v/>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D79" s="23" t="n">
+        <v>46321</v>
+      </c>
+      <c r="E79" t="n">
+        <v>3470745.49</v>
+      </c>
+      <c r="F79">
+        <f>E79-E78</f>
+        <v/>
+      </c>
+      <c r="G79">
+        <f>F79/E78</f>
+        <v/>
+      </c>
+      <c r="H79" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I79">
+        <f>F79/H79</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -3254,17 +3254,17 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -3272,21 +3272,21 @@
       <c r="D72" s="23" t="n">
         <v>46321</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72" s="3" t="n">
         <v>1265736.68</v>
       </c>
-      <c r="F72">
+      <c r="F72" s="3">
         <f>E72-E71</f>
         <v/>
       </c>
-      <c r="G72">
+      <c r="G72" s="3">
         <f>F72/E71</f>
         <v/>
       </c>
-      <c r="H72" t="n">
+      <c r="H72" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I72">
+      <c r="I72" s="3">
         <f>F72/H72</f>
         <v/>
       </c>
@@ -6267,17 +6267,17 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -6285,21 +6285,21 @@
       <c r="D79" s="23" t="n">
         <v>46321</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79" s="3" t="n">
         <v>1040601.66</v>
       </c>
-      <c r="F79">
+      <c r="F79" s="3">
         <f>E79-E78</f>
         <v/>
       </c>
-      <c r="G79">
+      <c r="G79" s="3">
         <f>F79/E78</f>
         <v/>
       </c>
-      <c r="H79" t="n">
+      <c r="H79" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I79">
+      <c r="I79" s="3">
         <f>F79/H79</f>
         <v/>
       </c>
@@ -9064,17 +9064,17 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -9082,21 +9082,21 @@
       <c r="D73" s="23" t="n">
         <v>46321</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" s="3" t="n">
         <v>3544698.77</v>
       </c>
-      <c r="F73">
+      <c r="F73" s="3">
         <f>E73-E72</f>
         <v/>
       </c>
-      <c r="G73">
+      <c r="G73" s="3">
         <f>F73/E72</f>
         <v/>
       </c>
-      <c r="H73" t="n">
+      <c r="H73" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I73">
+      <c r="I73" s="3">
         <f>F73/H73</f>
         <v/>
       </c>
@@ -12307,17 +12307,17 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -12325,21 +12325,21 @@
       <c r="D79" s="23" t="n">
         <v>46321</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79" s="3" t="n">
         <v>3470745.49</v>
       </c>
-      <c r="F79">
+      <c r="F79" s="3">
         <f>E79-E78</f>
         <v/>
       </c>
-      <c r="G79">
+      <c r="G79" s="3">
         <f>F79/E78</f>
         <v/>
       </c>
-      <c r="H79" t="n">
+      <c r="H79" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I79">
+      <c r="I79" s="3">
         <f>F79/H79</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -3288,6 +3288,44 @@
       </c>
       <c r="I72" s="3">
         <f>F72/H72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D73" s="23" t="n">
+        <v>46322</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1279146.68</v>
+      </c>
+      <c r="F73">
+        <f>E73-E72</f>
+        <v/>
+      </c>
+      <c r="G73">
+        <f>F73/E72</f>
+        <v/>
+      </c>
+      <c r="H73" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I73">
+        <f>F73/H73</f>
         <v/>
       </c>
     </row>
@@ -3302,7 +3340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6301,6 +6339,44 @@
       </c>
       <c r="I79" s="3">
         <f>F79/H79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D80" s="23" t="n">
+        <v>46322</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1039611.66</v>
+      </c>
+      <c r="F80">
+        <f>E80-E79</f>
+        <v/>
+      </c>
+      <c r="G80">
+        <f>F80/E79</f>
+        <v/>
+      </c>
+      <c r="H80" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I80">
+        <f>F80/H80</f>
         <v/>
       </c>
     </row>
@@ -6315,7 +6391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -9098,6 +9174,44 @@
       </c>
       <c r="I73" s="3">
         <f>F73/H73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D74" s="23" t="n">
+        <v>46322</v>
+      </c>
+      <c r="E74" t="n">
+        <v>3623808.77</v>
+      </c>
+      <c r="F74">
+        <f>E74-E73</f>
+        <v/>
+      </c>
+      <c r="G74">
+        <f>F74/E73</f>
+        <v/>
+      </c>
+      <c r="H74" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I74">
+        <f>F74/H74</f>
         <v/>
       </c>
     </row>
@@ -9200,7 +9314,7 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I2" s="13">
@@ -9241,11 +9355,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续8日增持</t>
+          <t>连续9日增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-8+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-9+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -9282,11 +9396,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续8日增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-8+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -9323,11 +9437,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续13日增持</t>
+          <t>连续14日增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-13+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-14+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -9342,7 +9456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12344,6 +12458,44 @@
         <v/>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D80" s="23" t="n">
+        <v>46322</v>
+      </c>
+      <c r="E80" t="n">
+        <v>3514445.49</v>
+      </c>
+      <c r="F80">
+        <f>E80-E79</f>
+        <v/>
+      </c>
+      <c r="G80">
+        <f>F80/E79</f>
+        <v/>
+      </c>
+      <c r="H80" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I80">
+        <f>F80/H80</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -3292,17 +3292,17 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -3310,21 +3310,21 @@
       <c r="D73" s="23" t="n">
         <v>46322</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" s="3" t="n">
         <v>1279146.68</v>
       </c>
-      <c r="F73">
+      <c r="F73" s="3">
         <f>E73-E72</f>
         <v/>
       </c>
-      <c r="G73">
+      <c r="G73" s="3">
         <f>F73/E72</f>
         <v/>
       </c>
-      <c r="H73" t="n">
+      <c r="H73" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I73">
+      <c r="I73" s="3">
         <f>F73/H73</f>
         <v/>
       </c>
@@ -6343,17 +6343,17 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -6361,21 +6361,21 @@
       <c r="D80" s="23" t="n">
         <v>46322</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80" s="3" t="n">
         <v>1039611.66</v>
       </c>
-      <c r="F80">
+      <c r="F80" s="3">
         <f>E80-E79</f>
         <v/>
       </c>
-      <c r="G80">
+      <c r="G80" s="3">
         <f>F80/E79</f>
         <v/>
       </c>
-      <c r="H80" t="n">
+      <c r="H80" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I80">
+      <c r="I80" s="3">
         <f>F80/H80</f>
         <v/>
       </c>
@@ -9178,17 +9178,17 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -9196,21 +9196,21 @@
       <c r="D74" s="23" t="n">
         <v>46322</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74" s="3" t="n">
         <v>3623808.77</v>
       </c>
-      <c r="F74">
+      <c r="F74" s="3">
         <f>E74-E73</f>
         <v/>
       </c>
-      <c r="G74">
+      <c r="G74" s="3">
         <f>F74/E73</f>
         <v/>
       </c>
-      <c r="H74" t="n">
+      <c r="H74" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I74">
+      <c r="I74" s="3">
         <f>F74/H74</f>
         <v/>
       </c>
@@ -12459,17 +12459,17 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -12477,21 +12477,21 @@
       <c r="D80" s="23" t="n">
         <v>46322</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80" s="3" t="n">
         <v>3514445.49</v>
       </c>
-      <c r="F80">
+      <c r="F80" s="3">
         <f>E80-E79</f>
         <v/>
       </c>
-      <c r="G80">
+      <c r="G80" s="3">
         <f>F80/E79</f>
         <v/>
       </c>
-      <c r="H80" t="n">
+      <c r="H80" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I80">
+      <c r="I80" s="3">
         <f>F80/H80</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -3326,6 +3326,44 @@
       </c>
       <c r="I73" s="3">
         <f>F73/H73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D74" s="23" t="n">
+        <v>46323</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1255656.68</v>
+      </c>
+      <c r="F74">
+        <f>E74-E73</f>
+        <v/>
+      </c>
+      <c r="G74">
+        <f>F74/E73</f>
+        <v/>
+      </c>
+      <c r="H74" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I74">
+        <f>F74/H74</f>
         <v/>
       </c>
     </row>
@@ -3340,7 +3378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6377,6 +6415,44 @@
       </c>
       <c r="I80" s="3">
         <f>F80/H80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D81" s="23" t="n">
+        <v>46323</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1075881.66</v>
+      </c>
+      <c r="F81">
+        <f>E81-E80</f>
+        <v/>
+      </c>
+      <c r="G81">
+        <f>F81/E80</f>
+        <v/>
+      </c>
+      <c r="H81" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I81">
+        <f>F81/H81</f>
         <v/>
       </c>
     </row>
@@ -6391,7 +6467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -9212,6 +9288,44 @@
       </c>
       <c r="I74" s="3">
         <f>F74/H74</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D75" s="23" t="n">
+        <v>46323</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3637758.77</v>
+      </c>
+      <c r="F75">
+        <f>E75-E74</f>
+        <v/>
+      </c>
+      <c r="G75">
+        <f>F75/E74</f>
+        <v/>
+      </c>
+      <c r="H75" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I75">
+        <f>F75/H75</f>
         <v/>
       </c>
     </row>
@@ -9314,7 +9428,7 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I2" s="13">
@@ -9355,11 +9469,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续9日增持</t>
+          <t>连续10日增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-9+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-10+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -9396,7 +9510,7 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I4" s="13">
@@ -9437,11 +9551,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续14日增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-14+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-1+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -9456,7 +9570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12496,6 +12610,44 @@
         <v/>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D81" s="23" t="n">
+        <v>46323</v>
+      </c>
+      <c r="E81" t="n">
+        <v>3490345.49</v>
+      </c>
+      <c r="F81">
+        <f>E81-E80</f>
+        <v/>
+      </c>
+      <c r="G81">
+        <f>F81/E80</f>
+        <v/>
+      </c>
+      <c r="H81" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I81">
+        <f>F81/H81</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -3330,17 +3330,17 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -3348,21 +3348,21 @@
       <c r="D74" s="23" t="n">
         <v>46323</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74" s="3" t="n">
         <v>1255656.68</v>
       </c>
-      <c r="F74">
+      <c r="F74" s="3">
         <f>E74-E73</f>
         <v/>
       </c>
-      <c r="G74">
+      <c r="G74" s="3">
         <f>F74/E73</f>
         <v/>
       </c>
-      <c r="H74" t="n">
+      <c r="H74" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I74">
+      <c r="I74" s="3">
         <f>F74/H74</f>
         <v/>
       </c>
@@ -6419,17 +6419,17 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -6437,21 +6437,21 @@
       <c r="D81" s="23" t="n">
         <v>46323</v>
       </c>
-      <c r="E81" t="n">
+      <c r="E81" s="3" t="n">
         <v>1075881.66</v>
       </c>
-      <c r="F81">
+      <c r="F81" s="3">
         <f>E81-E80</f>
         <v/>
       </c>
-      <c r="G81">
+      <c r="G81" s="3">
         <f>F81/E80</f>
         <v/>
       </c>
-      <c r="H81" t="n">
+      <c r="H81" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I81">
+      <c r="I81" s="3">
         <f>F81/H81</f>
         <v/>
       </c>
@@ -9292,17 +9292,17 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -9310,21 +9310,21 @@
       <c r="D75" s="23" t="n">
         <v>46323</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="3" t="n">
         <v>3637758.77</v>
       </c>
-      <c r="F75">
+      <c r="F75" s="3">
         <f>E75-E74</f>
         <v/>
       </c>
-      <c r="G75">
+      <c r="G75" s="3">
         <f>F75/E74</f>
         <v/>
       </c>
-      <c r="H75" t="n">
+      <c r="H75" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I75">
+      <c r="I75" s="3">
         <f>F75/H75</f>
         <v/>
       </c>
@@ -12611,17 +12611,17 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -12629,21 +12629,21 @@
       <c r="D81" s="23" t="n">
         <v>46323</v>
       </c>
-      <c r="E81" t="n">
+      <c r="E81" s="3" t="n">
         <v>3490345.49</v>
       </c>
-      <c r="F81">
+      <c r="F81" s="3">
         <f>E81-E80</f>
         <v/>
       </c>
-      <c r="G81">
+      <c r="G81" s="3">
         <f>F81/E80</f>
         <v/>
       </c>
-      <c r="H81" t="n">
+      <c r="H81" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I81">
+      <c r="I81" s="3">
         <f>F81/H81</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -3364,6 +3364,44 @@
       </c>
       <c r="I74" s="3">
         <f>F74/H74</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D75" s="23" t="n">
+        <v>46324</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1231986.68</v>
+      </c>
+      <c r="F75">
+        <f>E75-E74</f>
+        <v/>
+      </c>
+      <c r="G75">
+        <f>F75/E74</f>
+        <v/>
+      </c>
+      <c r="H75" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I75">
+        <f>F75/H75</f>
         <v/>
       </c>
     </row>
@@ -3378,7 +3416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6453,6 +6491,44 @@
       </c>
       <c r="I81" s="3">
         <f>F81/H81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D82" s="23" t="n">
+        <v>46324</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1152651.66</v>
+      </c>
+      <c r="F82">
+        <f>E82-E81</f>
+        <v/>
+      </c>
+      <c r="G82">
+        <f>F82/E81</f>
+        <v/>
+      </c>
+      <c r="H82" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I82">
+        <f>F82/H82</f>
         <v/>
       </c>
     </row>
@@ -6467,7 +6543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -9326,6 +9402,44 @@
       </c>
       <c r="I75" s="3">
         <f>F75/H75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D76" s="23" t="n">
+        <v>46324</v>
+      </c>
+      <c r="E76" t="n">
+        <v>3747558.77</v>
+      </c>
+      <c r="F76">
+        <f>E76-E75</f>
+        <v/>
+      </c>
+      <c r="G76">
+        <f>F76/E75</f>
+        <v/>
+      </c>
+      <c r="H76" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I76">
+        <f>F76/H76</f>
         <v/>
       </c>
     </row>
@@ -9428,11 +9542,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>连续2日减持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-1+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-2+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -9469,11 +9583,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续10日增持</t>
+          <t>连续11日增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-10+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-11+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -9510,11 +9624,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>连续2日增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -9551,7 +9665,7 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I5" s="13">
@@ -9570,7 +9684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12648,6 +12762,44 @@
         <v/>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D82" s="23" t="n">
+        <v>46324</v>
+      </c>
+      <c r="E82" t="n">
+        <v>3638445.49</v>
+      </c>
+      <c r="F82">
+        <f>E82-E81</f>
+        <v/>
+      </c>
+      <c r="G82">
+        <f>F82/E81</f>
+        <v/>
+      </c>
+      <c r="H82" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I82">
+        <f>F82/H82</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -3368,17 +3368,17 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -3386,21 +3386,21 @@
       <c r="D75" s="23" t="n">
         <v>46324</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="3" t="n">
         <v>1231986.68</v>
       </c>
-      <c r="F75">
+      <c r="F75" s="3">
         <f>E75-E74</f>
         <v/>
       </c>
-      <c r="G75">
+      <c r="G75" s="3">
         <f>F75/E74</f>
         <v/>
       </c>
-      <c r="H75" t="n">
+      <c r="H75" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I75">
+      <c r="I75" s="3">
         <f>F75/H75</f>
         <v/>
       </c>
@@ -6495,17 +6495,17 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -6513,21 +6513,21 @@
       <c r="D82" s="23" t="n">
         <v>46324</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E82" s="3" t="n">
         <v>1152651.66</v>
       </c>
-      <c r="F82">
+      <c r="F82" s="3">
         <f>E82-E81</f>
         <v/>
       </c>
-      <c r="G82">
+      <c r="G82" s="3">
         <f>F82/E81</f>
         <v/>
       </c>
-      <c r="H82" t="n">
+      <c r="H82" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I82">
+      <c r="I82" s="3">
         <f>F82/H82</f>
         <v/>
       </c>
@@ -9406,17 +9406,17 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -9424,21 +9424,21 @@
       <c r="D76" s="23" t="n">
         <v>46324</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76" s="3" t="n">
         <v>3747558.77</v>
       </c>
-      <c r="F76">
+      <c r="F76" s="3">
         <f>E76-E75</f>
         <v/>
       </c>
-      <c r="G76">
+      <c r="G76" s="3">
         <f>F76/E75</f>
         <v/>
       </c>
-      <c r="H76" t="n">
+      <c r="H76" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I76">
+      <c r="I76" s="3">
         <f>F76/H76</f>
         <v/>
       </c>
@@ -12763,17 +12763,17 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -12781,21 +12781,21 @@
       <c r="D82" s="23" t="n">
         <v>46324</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E82" s="3" t="n">
         <v>3638445.49</v>
       </c>
-      <c r="F82">
+      <c r="F82" s="3">
         <f>E82-E81</f>
         <v/>
       </c>
-      <c r="G82">
+      <c r="G82" s="3">
         <f>F82/E81</f>
         <v/>
       </c>
-      <c r="H82" t="n">
+      <c r="H82" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I82">
+      <c r="I82" s="3">
         <f>F82/H82</f>
         <v/>
       </c>
